--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$53</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="405">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -498,6 +498,22 @@
   <si>
     <t>Element `MedicationDispense.recorded` has a context of MedicationDispense based on following the parent source element upwards and mapping to `MedicationDispense`.
 Element `MedicationDispense.recorded` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
+  </si>
+  <si>
+    <t>MedicationDispense.extension:groupIdentifier</t>
+  </si>
+  <si>
+    <t>groupIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-group-identifier}
+</t>
+  </si>
+  <si>
+    <t>Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird.</t>
+  </si>
+  <si>
+    <t>AT ELGA e-Medikation Extension, die den e-Med GroupIdentifier beinhaltet.</t>
   </si>
   <si>
     <t>MedicationDispense.modifierExtension</t>
@@ -1605,7 +1621,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO52"/>
+  <dimension ref="A1:AO53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.03515625" customWidth="true" bestFit="true"/>
@@ -2946,43 +2962,41 @@
         <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3030,7 +3044,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3039,7 +3053,7 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>139</v>
@@ -3048,7 +3062,7 @@
         <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>21</v>
@@ -3060,46 +3074,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I13" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I13" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3147,7 +3163,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3159,30 +3175,30 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
-      <c r="A14" t="s" s="2">
-        <v>169</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3193,10 +3209,10 @@
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>21</v>
@@ -3205,15 +3221,17 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3262,7 +3280,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3277,27 +3295,27 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" hidden="true">
+      <c r="A15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AM14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3305,22 +3323,22 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>176</v>
@@ -3328,9 +3346,7 @@
       <c r="M15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3355,13 +3371,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3379,13 +3395,13 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
@@ -3394,27 +3410,27 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3422,30 +3438,32 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3470,32 +3488,34 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AC16" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>88</v>
@@ -3507,31 +3527,29 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3543,7 +3561,7 @@
         <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
@@ -3552,13 +3570,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3585,31 +3603,29 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AC17" s="2"/>
+      <c r="AD17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3624,10 +3640,10 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -3639,15 +3655,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>21</v>
@@ -3657,10 +3673,10 @@
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -3669,13 +3685,13 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3702,13 +3718,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3726,7 +3742,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3741,10 +3757,10 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
@@ -3758,12 +3774,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3784,17 +3802,15 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3819,13 +3835,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -3843,7 +3859,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3858,10 +3874,10 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
@@ -3873,12 +3889,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3886,31 +3902,31 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3936,13 +3952,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3960,10 +3976,10 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>88</v>
@@ -3975,27 +3991,27 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>216</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4018,16 +4034,16 @@
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4077,10 +4093,10 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>88</v>
@@ -4092,27 +4108,27 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
-      <c r="A22" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4120,30 +4136,32 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4192,7 +4210,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4207,27 +4225,27 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4250,13 +4268,13 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4307,13 +4325,13 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
@@ -4322,27 +4340,27 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>240</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
+      <c r="A24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AN23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4350,13 +4368,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
@@ -4365,13 +4383,13 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4422,7 +4440,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4437,27 +4455,27 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AM24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
-      <c r="A25" t="s" s="2">
-        <v>248</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4465,13 +4483,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
@@ -4480,13 +4498,13 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4537,25 +4555,25 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4569,21 +4587,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -4595,7 +4613,7 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>255</v>
@@ -4603,9 +4621,7 @@
       <c r="M26" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4660,19 +4676,19 @@
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
@@ -4686,14 +4702,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>259</v>
+        <v>159</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4706,10 +4722,10 @@
         <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>133</v>
@@ -4721,11 +4737,9 @@
         <v>261</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4791,7 +4805,7 @@
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4812,36 +4826,38 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>266</v>
+        <v>163</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4866,66 +4882,66 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AG28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AA28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4933,13 +4949,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -4948,16 +4964,18 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -4981,13 +4999,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5005,10 +5023,10 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>88</v>
@@ -5020,27 +5038,27 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AM29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" hidden="true">
-      <c r="A30" t="s" s="2">
-        <v>276</v>
-      </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5048,13 +5066,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -5063,13 +5081,13 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5120,10 +5138,10 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>88</v>
@@ -5135,7 +5153,7 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>280</v>
@@ -5166,7 +5184,7 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5186,9 +5204,7 @@
       <c r="M31" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N31" t="s" s="2">
-        <v>285</v>
-      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5225,14 +5241,16 @@
         <v>21</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>281</v>
@@ -5241,7 +5259,7 @@
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5250,31 +5268,29 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>289</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5283,10 +5299,10 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5295,16 +5311,16 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5342,19 +5358,17 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5369,30 +5383,30 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>21</v>
@@ -5414,16 +5428,16 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5473,7 +5487,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5488,35 +5502,37 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
@@ -5531,15 +5547,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>187</v>
+        <v>302</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5564,13 +5582,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>300</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>301</v>
+        <v>21</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5588,13 +5606,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -5603,27 +5621,27 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5646,13 +5664,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>306</v>
+        <v>192</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5679,13 +5697,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5703,7 +5721,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5721,24 +5739,24 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN35" t="s" s="2">
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO35" t="s" s="2">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="36" hidden="true">
-      <c r="A36" t="s" s="2">
-        <v>312</v>
-      </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5746,13 +5764,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
@@ -5761,13 +5779,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5818,7 +5836,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5836,13 +5854,13 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>316</v>
@@ -5873,16 +5891,16 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5951,24 +5969,24 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN37" t="s" s="2">
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5976,28 +5994,28 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6048,7 +6066,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6063,22 +6081,22 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>323</v>
-      </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>329</v>
       </c>
@@ -6091,13 +6109,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6106,7 +6124,7 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>330</v>
@@ -6178,27 +6196,27 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6221,13 +6239,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6278,13 +6296,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6296,24 +6314,24 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN40" t="s" s="2">
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AO40" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>341</v>
-      </c>
       <c r="B41" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6324,10 +6342,10 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6336,13 +6354,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6393,7 +6411,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6408,27 +6426,27 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AO41" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6451,17 +6469,15 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L42" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>352</v>
-      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6510,7 +6526,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6525,27 +6541,27 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" hidden="true">
-      <c r="A43" t="s" s="2">
-        <v>354</v>
-      </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6556,10 +6572,10 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6568,7 +6584,7 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>243</v>
+        <v>354</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>355</v>
@@ -6576,7 +6592,9 @@
       <c r="M43" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="N43" s="2"/>
+      <c r="N43" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6625,13 +6643,13 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -6643,13 +6661,13 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -6671,7 +6689,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6683,13 +6701,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>251</v>
+        <v>361</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6740,7 +6758,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>252</v>
+        <v>359</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6752,19 +6770,19 @@
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -6772,21 +6790,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6798,7 +6816,7 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>254</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>255</v>
@@ -6806,9 +6824,7 @@
       <c r="M45" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N45" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6863,19 +6879,19 @@
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6889,14 +6905,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>259</v>
+        <v>159</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6909,10 +6925,10 @@
         <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>133</v>
@@ -6924,11 +6940,9 @@
         <v>261</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6994,7 +7008,7 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -7008,42 +7022,46 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>363</v>
+        <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>364</v>
+        <v>265</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7091,25 +7109,25 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>362</v>
+        <v>267</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>366</v>
+        <v>131</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
@@ -7134,7 +7152,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>88</v>
@@ -7149,13 +7167,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>187</v>
+        <v>368</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7182,13 +7200,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>371</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7209,7 +7227,7 @@
         <v>367</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>88</v>
@@ -7224,24 +7242,24 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>302</v>
+        <v>371</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>372</v>
+        <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>373</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7252,7 +7270,7 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7264,13 +7282,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7297,13 +7315,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7321,13 +7339,13 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
@@ -7339,24 +7357,24 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>21</v>
+        <v>378</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7379,13 +7397,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>382</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7412,13 +7430,13 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>21</v>
+        <v>383</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -7436,7 +7454,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7454,13 +7472,13 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -7468,21 +7486,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>388</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -7494,17 +7512,15 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>392</v>
-      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7553,7 +7569,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7571,13 +7587,13 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>21</v>
+        <v>391</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -7585,14 +7601,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7611,16 +7627,16 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7670,7 +7686,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7688,20 +7704,137 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO52" t="s" s="2">
+      <c r="B53" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO52">
+  <autoFilter ref="A1:AO53">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7711,7 +7844,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI51">
+  <conditionalFormatting sqref="A2:AI52">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="422">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1141,7 +1141,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, wie das Medikament vom Patienten einzunehmen ist. 
+    <t>Gibt an, wie das abgegebene Arzneimittel vom Patienten einzunehmen ist. 
 Der Apotheker überprüft die Medikamentenverordnung vor der Abgabe und passt die Dosierungsanweisung gegebenenfalls auf Grundlage des tatsächlich abgegebenen Produkts an.</t>
   </si>
   <si>
@@ -1152,7 +1152,64 @@
 The pharmacist reviews the medication order prior to dispense and updates the dosageInstruction based on the actual product being dispensed.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:extension.value}
+</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+  </si>
+  <si>
+    <t>MedicationDispense.dosageInstruction:otherDosage</t>
+  </si>
+  <si>
+    <t>otherDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-other-administration}
+</t>
+  </si>
+  <si>
+    <t>How the medication is to be used by the patient or administered by the caregiver</t>
+  </si>
+  <si>
+    <t>MedicationDispense.dosageInstruction:timedDosage</t>
+  </si>
+  <si>
+    <t>timedDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-timed-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationDispense.dosageInstruction:frequencyDosage</t>
+  </si>
+  <si>
+    <t>frequencyDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-frequency-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationDispense.dosageInstruction:freitextDosage</t>
+  </si>
+  <si>
+    <t>freitextDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-freetext-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationDispense.dosageInstruction:standardDosage</t>
+  </si>
+  <si>
+    <t>standardDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-standard-administration}
+</t>
   </si>
   <si>
     <t>MedicationDispense.substitution</t>
@@ -1621,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO53"/>
+  <dimension ref="A1:AO58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.03515625" customWidth="true" bestFit="true"/>
@@ -6109,7 +6166,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
@@ -6556,7 +6613,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>353</v>
       </c>
@@ -6569,7 +6626,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>80</v>
@@ -6631,16 +6688,14 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>353</v>
@@ -6661,7 +6716,7 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6673,14 +6728,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6689,10 +6746,10 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -6701,15 +6758,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>248</v>
+        <v>362</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6758,13 +6817,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -6776,26 +6835,28 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6804,10 +6865,10 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -6816,15 +6877,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>254</v>
+        <v>366</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>255</v>
+        <v>363</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6873,25 +6936,25 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>257</v>
+        <v>353</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>258</v>
+        <v>359</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6903,16 +6966,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="D46" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6922,7 +6987,7 @@
         <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -6931,16 +6996,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>133</v>
+        <v>369</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>260</v>
+        <v>363</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>261</v>
+        <v>356</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>162</v>
+        <v>357</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6990,7 +7055,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>262</v>
+        <v>353</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7002,13 +7067,13 @@
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>258</v>
+        <v>359</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -7020,16 +7085,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D47" t="s" s="2">
-        <v>264</v>
+        <v>21</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7039,29 +7106,27 @@
         <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>133</v>
+        <v>372</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>265</v>
+        <v>363</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7109,7 +7174,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>267</v>
+        <v>353</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7121,13 +7186,13 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>131</v>
+        <v>359</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
@@ -7139,26 +7204,28 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7167,15 +7234,17 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7224,13 +7293,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -7242,7 +7311,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7256,10 +7325,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7270,7 +7339,7 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7282,13 +7351,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>192</v>
+        <v>248</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7315,31 +7384,31 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="Z49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7357,24 +7426,24 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>307</v>
+        <v>379</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>378</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7385,7 +7454,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7397,13 +7466,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>380</v>
+        <v>255</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>381</v>
+        <v>256</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7430,13 +7499,13 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -7454,31 +7523,31 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>379</v>
+        <v>257</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>384</v>
+        <v>258</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -7486,14 +7555,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7512,15 +7581,17 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>387</v>
+        <v>133</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>388</v>
+        <v>260</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7569,7 +7640,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>386</v>
+        <v>262</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7581,19 +7652,19 @@
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>390</v>
+        <v>258</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>391</v>
+        <v>21</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -7601,44 +7672,46 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>393</v>
+        <v>264</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>394</v>
+        <v>133</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>395</v>
+        <v>265</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>396</v>
+        <v>266</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7686,7 +7759,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>392</v>
+        <v>267</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7698,13 +7771,13 @@
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>398</v>
+        <v>131</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
@@ -7718,10 +7791,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7729,10 +7802,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7744,17 +7817,15 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7803,13 +7874,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -7821,20 +7892,599 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K56" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO53" t="s" s="2">
+      <c r="L56" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO53">
+  <autoFilter ref="A1:AO58">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7844,7 +8494,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI52">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,18 +462,19 @@
     <t>renderedDosageInstruction</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction}
 </t>
   </si>
   <si>
     <t>Vollständige Darstellung der Dosierungsanweisungen</t>
   </si>
   <si>
-    <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>
-  </si>
-  <si>
-    <t>Element `MedicationRequest.renderedDosageInstruction` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
-Element `MedicationRequest.renderedDosageInstruction` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
+    <t>R5: `MedicationDispense.renderedDosageInstruction` (new:markdown)</t>
+  </si>
+  <si>
+    <t>Element `MedicationDispense.renderedDosageInstruction` has a context of MedicationDispense based on following the parent source element upwards and mapping to `MedicationDispense`.
+Element `MedicationDispense.renderedDosageInstruction` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).
+The content of the renderedDosageInstructions must not be different than the dose represented in the dosageInstruction content.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -938,7 +939,7 @@
     <t>Maps to basedOn in Event logical model.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:reference.ofType(MedicationRequest).category}
+    <t xml:space="preserve">value:resolve().category}
 </t>
   </si>
   <si>
@@ -1708,7 +1709,7 @@
     <col min="25" max="25" width="117.7890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="43.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="21.1171875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -701,7 +701,7 @@
     <t>MedicationDispense.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-medikation) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -939,8 +939,8 @@
     <t>Maps to basedOn in Event logical model.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:resolve().category}
-</t>
+    <t>value:resolve().category.coding.system}
+value:resolve().category.coding.code}</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1709,7 +1709,7 @@
     <col min="25" max="25" width="117.7890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="21.1171875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="33.0546875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$56</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="415">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -406,18 +406,14 @@
     <t>MedicationDispense.contained</t>
   </si>
   <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
+    <t xml:space="preserve">Medication {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung}
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+    <t>TODO</t>
+  </si>
+  <si>
+    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
   </si>
   <si>
     <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
@@ -426,7 +422,7 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>ManufacturedProduct[classCode=ADMM]</t>
   </si>
   <si>
     <t>MedicationDispense.extension</t>
@@ -511,7 +507,7 @@
 </t>
   </si>
   <si>
-    <t>Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird.</t>
+    <t>Als groupIdentifier dient der e-Med GroupIdentifier der zugehörigen Geplanten Abgabe (wird auch im e-Rezept mitgeführt).</t>
   </si>
   <si>
     <t>AT ELGA e-Medikation Extension, die den e-Med GroupIdentifier beinhaltet.</t>
@@ -540,6 +536,9 @@
     <t>DomainResource.modifierExtension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>MedicationDispense.identifier</t>
   </si>
   <si>
@@ -547,7 +546,7 @@
 </t>
   </si>
   <si>
-    <t>Verpflichtende Angabe des 'e-Med Groupidentifiers' der Geplanten Abgabe, sofern diese existiert.</t>
+    <t>External identifier</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -575,7 +574,7 @@
 </t>
   </si>
   <si>
-    <t>Auslösendes Ereignis (Referenz auf Procedure-Ressource). Keine Verwendung in der Durchgeführten Abgabe.</t>
+    <t>Event that dispense is part of</t>
   </si>
   <si>
     <t>The procedure that trigger the dispense.</t>
@@ -621,66 +620,41 @@
   </si>
   <si>
     <t>MedicationDispense.statusReason[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+Reference(DetectedIssue|4.0.1)</t>
+  </si>
+  <si>
+    <t>Why a dispense was not performed</t>
+  </si>
+  <si>
+    <t>Indicates the reason why a dispense was not performed.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>A code describing why a dispense was not performed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.statusReason</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=RSON]/target[classCode=OBS,moodCode=EVN, code="not done reason"].value</t>
+  </si>
+  <si>
+    <t>MedicationDispense.category</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status, z.B. warum keine Abgabe erfolgte (zB. Produkt nicht verfügbar). Code oder Referenz (DetectedIssue)</t>
-  </si>
-  <si>
-    <t>Indicates the reason why a dispense was not performed.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>A code describing why a dispense was not performed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Event.statusReason</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RSON]/target[classCode=OBS,moodCode=EVN, code="not done reason"].value</t>
-  </si>
-  <si>
-    <t>MedicationDispense.statusReason[x]:statusReasonCodeableConcept</t>
-  </si>
-  <si>
-    <t>statusReasonCodeableConcept</t>
-  </si>
-  <si>
-    <t>Grund für den aktuellen Status als Code. (ex) https://hl7.org/fhir/R4/valueset-medicationdispense-status-reason.html</t>
-  </si>
-  <si>
-    <t>MedicationDispense.statusReason[x]:statusReasonReference</t>
-  </si>
-  <si>
-    <t>statusReasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
-</t>
-  </si>
-  <si>
-    <t>Referenz auf DetectedIssue-Ressource. Keine Verwendung in der Durchgeführten Abgabe.</t>
-  </si>
-  <si>
-    <t>MedicationDispense.category</t>
-  </si>
-  <si>
-    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant). Keine Verwendung in der Durchgeführten Abgabe.</t>
+    <t>Type of medication dispense</t>
   </si>
   <si>
     <t>Indicates the type of medication dispense (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -765,7 +739,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf Encounter oder EpisodeOfCare. Keine Verwendung in der Durchgeführten Abgabe.</t>
+    <t>Encounter / Episode associated with event</t>
   </si>
   <si>
     <t>The encounter or episode of care that establishes the context for this event.</t>
@@ -784,7 +758,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz (Any) auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der Durchgeführten Abgabe.</t>
+    <t>Information that supports the dispensing of the medication</t>
   </si>
   <si>
     <t>Additional information that supports the medication being dispensed.</t>
@@ -866,7 +840,7 @@
     <t>MedicationDispense.performer.function</t>
   </si>
   <si>
-    <t>Rolle der Person, die die Abgabe durchgeführt hat. Keine Verwendung in der Durchgeführten Abgabe.</t>
+    <t>Who performed the dispense and what they did</t>
   </si>
   <si>
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
@@ -912,7 +886,7 @@
 </t>
   </si>
   <si>
-    <t>Ort der Abgabe (Referenz auf Location Ressource). Keine Verwendung in durchgeführter Abgabe.</t>
+    <t>Where the dispense occurred</t>
   </si>
   <si>
     <t>The principal physical location where the dispense was performed.</t>
@@ -943,6 +917,9 @@
 value:resolve().category.coding.code}</t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
@@ -1024,7 +1001,7 @@
     <t>MedicationDispense.daysSupply</t>
   </si>
   <si>
-    <t>Tage, für die die abgegebene Menge ausreicht</t>
+    <t>Amount of medication expressed as a timing amount</t>
   </si>
   <si>
     <t>The amount of medication expressed as a timing amount.</t>
@@ -1046,7 +1023,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitpunkt, zu dem das Produkt verpackt und geprüft wurde.</t>
+    <t>When product was packaged and reviewed</t>
   </si>
   <si>
     <t>The time when the dispensed product was packaged and reviewed.</t>
@@ -1079,7 +1056,7 @@
     <t>MedicationDispense.destination</t>
   </si>
   <si>
-    <t>Ort an den das Medikament geschickt wurde (Referenz auf Location Ressource). Keine Verwendung in durchgeführter Abgabe.</t>
+    <t>Where the medication was sent</t>
   </si>
   <si>
     <t>Identification of the facility/location where the medication was shipped to, as part of the dispense event.</t>
@@ -1101,7 +1078,7 @@
 </t>
   </si>
   <si>
-    <t>Person, die das Medikament abgeholt hat. Referenz auf Patient oder Practitioner. Keine Verwendung in durchgeführter Abgabe.</t>
+    <t>Who collected the medication</t>
   </si>
   <si>
     <t>Identifies the person who picked up the medication.  This will usually be a patient or their caregiver, but some cases exist where it can be a healthcare professional.</t>
@@ -1679,13 +1656,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO58"/>
+  <dimension ref="A1:AO56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.03515625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.87890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.2578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="25.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="28.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -1964,7 +1941,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1977,13 +1954,13 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>21</v>
@@ -2081,7 +2058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -2100,7 +2077,7 @@
         <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -2212,7 +2189,7 @@
         <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -2430,7 +2407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2449,7 +2426,7 @@
         <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -2547,7 +2524,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2556,7 +2533,7 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2566,7 +2543,7 @@
         <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
@@ -2575,16 +2552,16 @@
         <v>21</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2634,7 +2611,7 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -2652,7 +2629,7 @@
         <v>21</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>21</v>
@@ -2666,10 +2643,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2692,13 +2669,13 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2737,17 +2714,17 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2759,7 +2736,7 @@
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
@@ -2779,13 +2756,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C10" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
@@ -2807,16 +2784,16 @@
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2866,7 +2843,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2875,10 +2852,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -2898,13 +2875,13 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C11" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>21</v>
@@ -2926,16 +2903,16 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2985,7 +2962,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2994,10 +2971,10 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -3017,13 +2994,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
@@ -3045,13 +3022,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3102,7 +3079,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3111,10 +3088,10 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -3134,14 +3111,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3160,19 +3137,19 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -3221,7 +3198,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3233,13 +3210,13 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
@@ -3251,7 +3228,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>165</v>
       </c>
@@ -3267,10 +3244,10 @@
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>21</v>
@@ -3616,7 +3593,7 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3673,14 +3650,16 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>191</v>
@@ -3698,31 +3677,29 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
+      <c r="A18" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>202</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>21</v>
       </c>
@@ -3731,10 +3708,10 @@
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -3743,15 +3720,17 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3776,13 +3755,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3800,7 +3779,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3815,10 +3794,10 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
@@ -3830,45 +3809,45 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3917,10 +3896,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>88</v>
@@ -3932,27 +3911,27 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>21</v>
+        <v>217</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3960,31 +3939,31 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4010,13 +3989,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4034,7 +4013,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4049,27 +4028,27 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4077,32 +4056,30 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4151,10 +4128,10 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>88</v>
@@ -4166,27 +4143,27 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4194,32 +4171,30 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4268,13 +4243,13 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
@@ -4283,27 +4258,27 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>234</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4311,13 +4286,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -4326,13 +4301,13 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4383,13 +4358,13 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
@@ -4398,10 +4373,10 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4415,10 +4390,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4429,7 +4404,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
@@ -4441,13 +4416,13 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4498,28 +4473,28 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
@@ -4528,26 +4503,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
@@ -4556,15 +4531,17 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>132</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4613,7 +4590,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4625,13 +4602,13 @@
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4645,42 +4622,46 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>21</v>
+        <v>256</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>254</v>
+        <v>132</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4728,25 +4709,25 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>258</v>
+        <v>164</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
@@ -4760,21 +4741,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -4786,18 +4767,18 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4821,13 +4802,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>265</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4845,25 +4826,25 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4875,48 +4856,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>264</v>
+        <v>21</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>133</v>
+        <v>268</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4967,22 +4944,22 @@
         <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>131</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
@@ -4996,10 +4973,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5022,18 +4999,16 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>274</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>271</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5057,31 +5032,31 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="Z29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5099,7 +5074,7 @@
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -5111,12 +5086,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5124,13 +5099,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -5139,15 +5114,17 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5184,25 +5161,23 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5211,29 +5186,31 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5242,10 +5219,10 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5254,15 +5231,17 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L31" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5311,13 +5290,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5326,29 +5305,31 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>285</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5357,10 +5338,10 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5369,16 +5350,16 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5416,17 +5397,19 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5441,19 +5424,19 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33">
@@ -5461,17 +5444,15 @@
         <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
@@ -5486,17 +5467,15 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>290</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5521,13 +5500,13 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -5545,13 +5524,13 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -5560,37 +5539,35 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
@@ -5605,17 +5582,15 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5664,13 +5639,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -5679,27 +5654,27 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>295</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5707,13 +5682,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5722,13 +5697,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>192</v>
+        <v>304</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5755,13 +5730,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5779,7 +5754,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5797,24 +5772,24 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5822,28 +5797,28 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5894,7 +5869,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5912,24 +5887,24 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5940,10 +5915,10 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5952,13 +5927,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6009,7 +5984,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6024,16 +5999,16 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>321</v>
@@ -6041,10 +6016,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6064,16 +6039,16 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6124,7 +6099,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6142,24 +6117,24 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6170,10 +6145,10 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6182,13 +6157,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6239,13 +6214,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6254,27 +6229,27 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6285,10 +6260,10 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6297,13 +6272,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>282</v>
+        <v>340</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6354,13 +6329,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6369,27 +6344,27 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>338</v>
+        <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6397,13 +6372,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6412,15 +6387,17 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6457,19 +6434,17 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6487,13 +6462,13 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>345</v>
+        <v>21</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6501,12 +6476,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="C42" s="2"/>
+      <c r="C42" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6527,15 +6504,17 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="M42" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N42" s="2"/>
+      <c r="N42" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6599,10 +6578,10 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6611,23 +6590,25 @@
         <v>21</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>352</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>80</v>
@@ -6642,16 +6623,16 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6689,17 +6670,19 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6717,7 +6700,7 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6734,7 +6717,7 @@
         <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>361</v>
@@ -6762,13 +6745,13 @@
         <v>362</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6818,7 +6801,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6836,7 +6819,7 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6850,13 +6833,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C45" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>21</v>
@@ -6878,16 +6861,16 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6937,7 +6920,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6955,7 +6938,7 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6969,13 +6952,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>21</v>
@@ -6997,16 +6980,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7056,7 +7039,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7074,7 +7057,7 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -7086,16 +7069,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7104,10 +7085,10 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
@@ -7116,17 +7097,15 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>372</v>
+        <v>240</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7175,13 +7154,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7193,28 +7172,26 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C48" t="s" s="2">
         <v>374</v>
       </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7223,10 +7200,10 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7235,17 +7212,15 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>375</v>
+        <v>246</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>363</v>
+        <v>247</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7294,25 +7269,25 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>353</v>
+        <v>249</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>359</v>
+        <v>250</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7326,21 +7301,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7352,15 +7327,17 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>248</v>
+        <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7409,31 +7386,31 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>376</v>
+        <v>254</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>379</v>
+        <v>250</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -7441,42 +7418,46 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>21</v>
+        <v>256</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>254</v>
+        <v>132</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7524,25 +7505,25 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>258</v>
+        <v>164</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
@@ -7556,21 +7537,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -7582,17 +7563,15 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>133</v>
+        <v>378</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>260</v>
+        <v>379</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7641,25 +7620,25 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>262</v>
+        <v>377</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>258</v>
+        <v>381</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7673,46 +7652,42 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>264</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>265</v>
+        <v>383</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7736,13 +7711,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>21</v>
+        <v>385</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7760,42 +7735,42 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>267</v>
+        <v>382</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>131</v>
+        <v>300</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>21</v>
+        <v>387</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7803,10 +7778,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7818,13 +7793,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>385</v>
+        <v>201</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7851,13 +7826,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -7875,13 +7850,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -7893,13 +7868,13 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -7907,10 +7882,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7921,7 +7896,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -7933,13 +7908,13 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>192</v>
+        <v>397</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7966,13 +7941,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>393</v>
+        <v>21</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7990,13 +7965,13 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
@@ -8008,35 +7983,35 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>307</v>
+        <v>400</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>395</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>21</v>
+        <v>403</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -8048,15 +8023,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>404</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8081,13 +8058,13 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>399</v>
+        <v>21</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>400</v>
+        <v>21</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -8105,7 +8082,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8123,13 +8100,13 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>402</v>
+        <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -8137,10 +8114,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8151,7 +8128,7 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -8163,15 +8140,17 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8220,7 +8199,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8238,254 +8217,20 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO58" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO58">
+  <autoFilter ref="A1:AO56">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8495,7 +8240,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI57">
+  <conditionalFormatting sqref="A2:AI55">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="417">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -989,6 +989,10 @@
     <t>The amount of medication that has been dispensed. Includes unit of measure.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+  </si>
+  <si>
     <t>.quantity</t>
   </si>
   <si>
@@ -1188,6 +1192,10 @@
   <si>
     <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-standard-administration}
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+frequencySameAsWhenCount:wenn .when verwendet wird und periodUnit = d muss die frequency mit der Anzahl an entries in .when übereinstimmen {(timing.repeat.when.exists() and timing.repeat.periodUnit = 'd') implies timing.repeat.when.distinct().count() = timing.repeat.frequency}weekdaysRequireWeeklyPeriod:DayOfWeek kann nur dann verwendet werden, wenn periodUnit 'wk' ist. {timing.repeat.dayOfWeek.exists() implies timing.repeat.periodUnit = 'wk'}frequencyEqualsEventWeekdayProduct:Wenn Wochentage angegeben sind dann entspricht die frequency dem Produkt aus Wochentagen und der Anzahl an ausgewählten Tageszeiten. {timing.repeat.when.exists() and timing.repeat.dayOfWeek.exists() implies timing.repeat.frequency = timing.repeat.when.distinct().count() * timing.repeat.dayOfWeek.distinct().count()}noDuplicateWhen:Tageszeiten können nicht mehrmals vorkommen. {timing.repeat.when.count() = timing.repeat.when.distinct().count()}noDuplicateDayOfWeek:Wochentage können nicht mehrmals vorkommen. {timing.repeat.dayOfWeek.count() = timing.repeat.dayOfWeek.distinct().count()}allowedPeriodUnitsForStandardAdministration:Für Standarddosierungen im Tageszeitenschema sind nur tägliche, wöchentliche oder monatliche Wiederholungen zulässig. {timing.repeat.periodUnit = 'd' or timing.repeat.periodUnit = 'wk' or timing.repeat.periodUnit = 'm'}</t>
   </si>
   <si>
     <t>MedicationDispense.substitution</t>
@@ -5651,30 +5659,30 @@
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>307</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5700,10 +5708,10 @@
         <v>304</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5754,7 +5762,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5766,13 +5774,13 @@
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>307</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
@@ -5781,15 +5789,15 @@
         <v>21</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5812,13 +5820,13 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5869,7 +5877,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5887,24 +5895,24 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5927,13 +5935,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5984,7 +5992,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5999,27 +6007,27 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6045,10 +6053,10 @@
         <v>274</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6099,7 +6107,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6117,24 +6125,24 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6157,13 +6165,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6214,7 +6222,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6232,13 +6240,13 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6246,10 +6254,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6272,13 +6280,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6329,7 +6337,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6344,10 +6352,10 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -6356,15 +6364,15 @@
         <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6387,16 +6395,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6434,7 +6442,7 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -6444,7 +6452,7 @@
         <v>284</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6462,7 +6470,7 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
@@ -6476,13 +6484,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>21</v>
@@ -6504,16 +6512,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6563,7 +6571,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6581,7 +6589,7 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6595,13 +6603,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>21</v>
@@ -6623,16 +6631,16 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6682,7 +6690,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6700,7 +6708,7 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6714,13 +6722,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>21</v>
@@ -6742,16 +6750,16 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6801,7 +6809,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6819,7 +6827,7 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6833,13 +6841,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>21</v>
@@ -6861,16 +6869,16 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6920,7 +6928,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6938,7 +6946,7 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6952,13 +6960,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>21</v>
@@ -6980,16 +6988,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7039,7 +7047,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7051,13 +7059,13 @@
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -7071,10 +7079,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7100,10 +7108,10 @@
         <v>240</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7154,7 +7162,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7172,13 +7180,13 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7186,10 +7194,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7301,10 +7309,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7418,10 +7426,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7537,10 +7545,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7563,13 +7571,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7620,7 +7628,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>88</v>
@@ -7638,7 +7646,7 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7652,10 +7660,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7681,10 +7689,10 @@
         <v>201</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7714,10 +7722,10 @@
         <v>195</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7735,7 +7743,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7759,18 +7767,18 @@
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7796,10 +7804,10 @@
         <v>201</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7829,10 +7837,10 @@
         <v>195</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -7850,7 +7858,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7868,13 +7876,13 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -7882,10 +7890,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7908,13 +7916,13 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7965,7 +7973,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7983,13 +7991,13 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>21</v>
@@ -7997,14 +8005,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8023,16 +8031,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8082,7 +8090,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8100,7 +8108,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -8114,10 +8122,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8140,16 +8148,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8199,7 +8207,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8217,7 +8225,7 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>88</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$68</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="472">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -298,7 +298,7 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
+    <t>Technische id der Ressource</t>
   </si>
   <si>
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
@@ -330,14 +330,191 @@
 </t>
   </si>
   <si>
-    <t>MedicationDispense.implicitRules</t>
+    <t>MedicationDispense.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationDispense.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationDispense.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>MedicationDispense.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>MedicationDispense.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>MedicationDispense.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>MedicationDispense.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>MedicationDispense.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>MedicationDispense.implicitRules</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -403,6 +580,59 @@
     <t>Act.text?</t>
   </si>
   <si>
+    <t>MedicationDispense.text.id</t>
+  </si>
+  <si>
+    <t>MedicationDispense.text.extension</t>
+  </si>
+  <si>
+    <t>MedicationDispense.text.status</t>
+  </si>
+  <si>
+    <t>generated | extensions | additional | empty</t>
+  </si>
+  <si>
+    <t>The status of the narrative - whether it's entirely generated (from just the defined data or the extensions too), or whether a human authored it and it may contain additional data.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The status of a resource narrative.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/narrative-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Narrative.status</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>MedicationDispense.text.div</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xhtml
+</t>
+  </si>
+  <si>
+    <t>Limited xhtml content</t>
+  </si>
+  <si>
+    <t>The actual narrative content, a stripped down version of XHTML.</t>
+  </si>
+  <si>
+    <t>The contents of the html element are an XHTML fragment containing only the basic html formatting elements described in chapters 7-11 and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained stylesheets. The XHTML content SHALL NOT contain a head, a body, external stylesheet references, scripts, forms, base/link/xlink, frames, iframes and objects.</t>
+  </si>
+  <si>
+    <t>Narrative.div</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+txt-1:The narrative SHALL contain only the basic html formatting elements and attributes described in chapters 7-11 (except section 4 of chapter 9) and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained style attributes {htmlChecks()}txt-2:The narrative SHALL have some non-whitespace content {htmlChecks()}</t>
+  </si>
+  <si>
     <t>MedicationDispense.contained</t>
   </si>
   <si>
@@ -428,28 +658,13 @@
     <t>MedicationDispense.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
     <t>Extension</t>
   </si>
   <si>
     <t>An Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationDispense.extension:renderedDosageInstruction</t>
@@ -516,27 +731,10 @@
     <t>MedicationDispense.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>MedicationDispense.identifier</t>
@@ -598,9 +796,6 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>A coded concept specifying the state of the dispense event.</t>
   </si>
   <si>
@@ -632,9 +827,6 @@
     <t>Indicates the reason why a dispense was not performed.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>A code describing why a dispense was not performed.</t>
   </si>
   <si>
@@ -792,32 +984,7 @@
     <t>MedicationDispense.performer.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>MedicationDispense.performer.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>MedicationDispense.performer.modifierExtension</t>
@@ -832,6 +999,9 @@
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1664,7 +1834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO56"/>
+  <dimension ref="A1:AO68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.87890625" customWidth="true" bestFit="true"/>
@@ -1695,7 +1865,7 @@
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="33.0546875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
@@ -2197,16 +2367,16 @@
         <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>102</v>
@@ -2217,9 +2387,7 @@
       <c r="M5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -2268,7 +2436,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
@@ -2280,13 +2448,13 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>21</v>
@@ -2307,14 +2475,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2326,16 +2494,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2361,49 +2529,49 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>21</v>
@@ -2417,14 +2585,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2440,10 +2608,10 @@
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>119</v>
@@ -2520,7 +2688,7 @@
         <v>21</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>21</v>
@@ -2534,10 +2702,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2548,7 +2716,7 @@
         <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>89</v>
@@ -2557,19 +2725,19 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2619,25 +2787,25 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>21</v>
@@ -2651,10 +2819,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2662,11 +2830,11 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
       </c>
@@ -2674,18 +2842,20 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -2722,86 +2892,86 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="AC9" s="2"/>
-      <c r="AD9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" hidden="true">
-      <c r="A10" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2851,7 +3021,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2860,10 +3030,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -2883,23 +3053,21 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2908,19 +3076,19 @@
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2946,13 +3114,13 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
@@ -2970,7 +3138,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2979,10 +3147,10 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -3002,14 +3170,12 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3018,7 +3184,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
@@ -3027,18 +3193,20 @@
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
@@ -3063,13 +3231,13 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -3087,7 +3255,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3096,10 +3264,10 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -3119,21 +3287,21 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -3142,10 +3310,10 @@
         <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>159</v>
@@ -3156,9 +3324,7 @@
       <c r="N13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="O13" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3206,25 +3372,25 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
@@ -3238,10 +3404,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3252,7 +3418,7 @@
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -3264,16 +3430,16 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3299,13 +3465,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3323,13 +3489,13 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>21</v>
@@ -3338,41 +3504,41 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AN14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
-      <c r="A15" t="s" s="2">
-        <v>174</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -3381,15 +3547,17 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3438,13 +3606,13 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
@@ -3453,7 +3621,7 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>179</v>
@@ -3468,7 +3636,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>180</v>
       </c>
@@ -3481,32 +3649,30 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>103</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3531,13 +3697,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3555,10 +3721,10 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>88</v>
@@ -3567,19 +3733,19 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>21</v>
@@ -3587,21 +3753,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3613,15 +3779,17 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>110</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3646,49 +3814,49 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>199</v>
+        <v>106</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -3700,12 +3868,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3713,13 +3881,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -3728,17 +3896,15 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3763,13 +3929,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3787,10 +3953,10 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>88</v>
@@ -3805,7 +3971,7 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
@@ -3819,10 +3985,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3842,19 +4008,19 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3904,7 +4070,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>88</v>
@@ -3916,30 +4082,30 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>196</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>21</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>216</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>217</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3947,10 +4113,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>89</v>
@@ -3959,19 +4125,19 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4021,42 +4187,42 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4064,10 +4230,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -4079,13 +4245,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>228</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4124,37 +4290,35 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -4168,12 +4332,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4182,7 +4348,7 @@
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -4194,15 +4360,17 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4251,7 +4419,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4260,19 +4428,19 @@
         <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4281,14 +4449,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4300,7 +4470,7 @@
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -4309,15 +4479,17 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4366,7 +4538,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4375,16 +4547,16 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4398,12 +4570,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4424,13 +4598,13 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4481,25 +4655,25 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -4513,43 +4687,41 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4598,7 +4770,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4610,13 +4782,13 @@
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4630,46 +4802,44 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>256</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>132</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4717,7 +4887,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4729,19 +4899,19 @@
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>164</v>
+        <v>235</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>21</v>
@@ -4749,10 +4919,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4763,7 +4933,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -4775,18 +4945,16 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>263</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4810,13 +4978,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>264</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4834,13 +5002,13 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
@@ -4849,10 +5017,10 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4866,10 +5034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4886,21 +5054,23 @@
         <v>89</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>268</v>
+        <v>164</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4925,13 +5095,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4949,7 +5119,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>88</v>
@@ -4964,16 +5134,16 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>21</v>
+        <v>253</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>21</v>
@@ -4981,10 +5151,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5007,13 +5177,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5040,13 +5210,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>21</v>
+        <v>258</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5064,7 +5234,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5079,10 +5249,10 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -5096,10 +5266,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5110,7 +5280,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5122,16 +5292,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5157,35 +5327,37 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>21</v>
+        <v>267</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AC30" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5194,37 +5366,35 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>285</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>288</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -5236,19 +5406,19 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5298,13 +5468,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5313,37 +5483,35 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>88</v>
@@ -5355,19 +5523,19 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5417,13 +5585,13 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
@@ -5438,21 +5606,21 @@
         <v>286</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>288</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5460,13 +5628,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -5475,13 +5643,13 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>201</v>
+        <v>290</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5508,13 +5676,13 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>299</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -5532,7 +5700,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5547,27 +5715,27 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>21</v>
+        <v>293</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>301</v>
+        <v>21</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>302</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5575,13 +5743,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
@@ -5590,13 +5758,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5647,42 +5815,42 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>307</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>21</v>
+        <v>300</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>309</v>
+        <v>21</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>310</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5690,13 +5858,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5705,13 +5873,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5762,25 +5930,25 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>307</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
@@ -5789,15 +5957,15 @@
         <v>21</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5808,7 +5976,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -5817,16 +5985,16 @@
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>317</v>
+        <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>318</v>
+        <v>103</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>319</v>
+        <v>104</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5877,7 +6045,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>105</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5889,44 +6057,44 @@
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>320</v>
+        <v>106</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5935,15 +6103,17 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>317</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>110</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5992,74 +6162,78 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>116</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>326</v>
+        <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>327</v>
+        <v>106</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>21</v>
+        <v>310</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>274</v>
+        <v>109</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6107,42 +6281,42 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>331</v>
+        <v>189</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6153,7 +6327,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6165,16 +6339,18 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>335</v>
+        <v>263</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6198,13 +6374,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>319</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6222,13 +6398,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6240,13 +6416,13 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6254,10 +6430,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6265,10 +6441,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>89</v>
@@ -6280,13 +6456,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6337,13 +6513,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6352,10 +6528,10 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -6364,15 +6540,15 @@
         <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6380,13 +6556,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6395,17 +6571,15 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6442,23 +6616,25 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -6470,7 +6646,7 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
@@ -6482,16 +6658,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6503,7 +6677,7 @@
         <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6512,16 +6686,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6559,19 +6733,17 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6586,30 +6758,30 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>21</v>
+        <v>340</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>21</v>
@@ -6619,7 +6791,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>89</v>
@@ -6631,16 +6803,16 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6690,7 +6862,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6705,30 +6877,30 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>21</v>
+        <v>340</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>21</v>
@@ -6738,7 +6910,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>89</v>
@@ -6750,16 +6922,16 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6809,7 +6981,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6824,40 +6996,38 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>21</v>
+        <v>340</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>89</v>
@@ -6869,17 +7039,15 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>366</v>
+        <v>263</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6904,13 +7072,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -6928,13 +7096,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -6946,37 +7114,35 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>89</v>
@@ -6988,17 +7154,15 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7047,42 +7211,42 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7105,13 +7269,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>240</v>
+        <v>359</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7162,7 +7326,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7174,30 +7338,30 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>362</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7208,7 +7372,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7217,16 +7381,16 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>246</v>
+        <v>372</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>247</v>
+        <v>373</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>248</v>
+        <v>374</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7277,7 +7441,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>249</v>
+        <v>371</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7289,44 +7453,44 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7335,17 +7499,15 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>132</v>
+        <v>372</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>252</v>
+        <v>379</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7394,78 +7556,74 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>254</v>
+        <v>378</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>381</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>250</v>
+        <v>382</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>256</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>132</v>
+        <v>329</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>257</v>
+        <v>384</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7513,42 +7671,42 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>259</v>
+        <v>383</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>164</v>
+        <v>386</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>21</v>
+        <v>387</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7556,10 +7714,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -7571,13 +7729,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7628,13 +7786,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -7646,24 +7804,24 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>21</v>
+        <v>394</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7674,10 +7832,10 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
@@ -7686,13 +7844,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>201</v>
+        <v>396</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7719,13 +7877,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>387</v>
+        <v>21</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>388</v>
+        <v>21</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7743,13 +7901,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -7758,27 +7916,27 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>21</v>
+        <v>399</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7786,13 +7944,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
@@ -7801,15 +7959,17 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>201</v>
+        <v>403</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7834,31 +7994,29 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>394</v>
+        <v>21</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7876,26 +8034,28 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>21</v>
       </c>
@@ -7907,7 +8067,7 @@
         <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -7916,15 +8076,17 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -7973,7 +8135,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7991,38 +8153,40 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C55" s="2"/>
+      <c r="C55" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="D55" t="s" s="2">
-        <v>405</v>
+        <v>21</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -8031,16 +8195,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8090,7 +8254,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8108,7 +8272,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -8120,14 +8284,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8136,10 +8302,10 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -8148,16 +8314,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L56" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="M56" t="s" s="2">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8207,7 +8373,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8225,7 +8391,7 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
@@ -8234,11 +8400,1409 @@
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO56">
+  <autoFilter ref="A1:AO68">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8248,7 +9812,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI55">
+  <conditionalFormatting sqref="A2:AI67">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,11 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Dokumentiert eine "Durchgeführte Abgabe" eines Arzneimittels ("MedicationDispense"-Ressource). 
-Die "Durchgeführte Abgabe" enthält die abgegebene Medikation und deren Dosierung und dient somit der Nachvollziehbarkeit der abgegebenen Arzneimittel in der e-Medikation. 
-Es können Abweichungen zur "Geplanten Abgabe" hinsichtlich des Medikaments und dessen Dosierung dokumentiert werden.
-Sofern eine zugehörige "Geplanten Abgabe" vorliegt, muss diese mit dem zugehörigen Planeintrag referenziert werden. Eine mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige "Geplante Abgabe", ersichtlich.
-Der aktuelle Status einer "Durchgeführten Abgabe" wird mittels "status"- und "type"-Element dokumentiert. Es werden R5-Backport-Extensions verwendet.</t>
+    <t>Profil einer "Durchgeführten Abgabe" eines Arzneimittels aus dem Medikationsplan.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -269,7 +265,7 @@
 </t>
   </si>
   <si>
-    <t>Durchgeführte Abgabe eines Arzneimittels mit oder ohne Bezug zur geplanten Abgabe. Verwendet R5 Backport Extensions.</t>
+    <t>Dispensing a medication to a named patient</t>
   </si>
   <si>
     <t>Indicates that a medication product is to be or has been dispensed for a named person/patient.  This includes a description of the medication product (supply) provided and the instructions for administering the medication.  The medication dispense is the result of a pharmacy system responding to a medication order.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2576" uniqueCount="478">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -708,6 +708,26 @@
 Element `MedicationDispense.recorded` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
+    <t>MedicationDispense.extension:statusChanged</t>
+  </si>
+  <si>
+    <t>statusChanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.statusChanged}
+</t>
+  </si>
+  <si>
+    <t>Datum der Statusänderung. Dies ist nur bei einem Status von: cancelled | entered-in-error | stopped relevant.</t>
+  </si>
+  <si>
+    <t>R5: `MedicationDispense.statusChanged` (new:dateTime)</t>
+  </si>
+  <si>
+    <t>Element `MedicationDispense.statusChanged` has a context of MedicationDispense based on following the parent source element upwards and mapping to `MedicationDispense`.
+Element `MedicationDispense.statusChanged` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
+  </si>
+  <si>
     <t>MedicationDispense.extension:groupIdentifier</t>
   </si>
   <si>
@@ -783,7 +803,7 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>Status der Durchgeführten Abgabe. Mögliche Ausprägungen: [completed | entered-in-error | stopped] Bedeutung: completed: Die Durchgeführte Abgabe ist abgeschlossen. | entered-in-error: Die Durchgeführte Abgabe wird aufgrund falscher Eingabe storniert. | stopped: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt).</t>
+    <t>Status der Durchgeführten Abgabe. Mögliche Ausprägungen: [completed | cancelled | entered-in-error ] Bedeutung: completed: Die Durchgeführte Abgabe ist abgeschlossen. | cancelled: Leerabgabe | entered-in-error: Die Durchgeführte Abgabe wird aufgrund falscher Eingabe storniert.</t>
   </si>
   <si>
     <t>A code specifying the state of the set of dispense events.</t>
@@ -1830,7 +1850,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO68"/>
+  <dimension ref="A1:AO69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.87890625" customWidth="true" bestFit="true"/>
@@ -4602,7 +4622,9 @@
       <c r="M24" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N24" s="2"/>
+      <c r="N24" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4683,12 +4705,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4697,25 +4721,25 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>109</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4766,7 +4790,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4775,7 +4799,7 @@
         <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>117</v>
@@ -4798,10 +4822,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4818,23 +4842,21 @@
         <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4883,7 +4905,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4895,19 +4917,19 @@
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>234</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>21</v>
@@ -4915,10 +4937,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4941,15 +4963,17 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4998,7 +5022,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5013,22 +5037,22 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AO27" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>244</v>
       </c>
@@ -5041,32 +5065,30 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>164</v>
+        <v>245</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N28" t="s" s="2">
         <v>247</v>
       </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5091,13 +5113,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5118,10 +5140,10 @@
         <v>244</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
@@ -5130,27 +5152,27 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" hidden="true">
-      <c r="A29" t="s" s="2">
-        <v>254</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5158,30 +5180,32 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>255</v>
+        <v>164</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5206,13 +5230,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5230,10 +5254,10 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>88</v>
@@ -5245,16 +5269,16 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>21</v>
+        <v>258</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5262,10 +5286,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5288,17 +5312,15 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>266</v>
-      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5323,13 +5345,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5347,7 +5369,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5362,10 +5384,10 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
@@ -5377,12 +5399,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5390,31 +5412,31 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5440,13 +5462,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5464,10 +5486,10 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>88</v>
@@ -5479,27 +5501,27 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>276</v>
-      </c>
       <c r="AM31" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5522,16 +5544,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5581,10 +5603,10 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>88</v>
@@ -5596,27 +5618,27 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL32" t="s" s="2">
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
-      <c r="A33" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="B33" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5624,30 +5646,32 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5696,7 +5720,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5711,19 +5735,19 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -5817,7 +5841,7 @@
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -5826,13 +5850,13 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>300</v>
+        <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
@@ -5841,7 +5865,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>301</v>
       </c>
@@ -5854,13 +5878,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5941,14 +5965,14 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5956,7 +5980,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>307</v>
       </c>
@@ -5969,13 +5993,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
@@ -5984,13 +6008,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>102</v>
+        <v>308</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>103</v>
+        <v>309</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>104</v>
+        <v>310</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6041,25 +6065,25 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>105</v>
+        <v>307</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>21</v>
+        <v>311</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>106</v>
+        <v>312</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
@@ -6073,21 +6097,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -6099,17 +6123,15 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6158,19 +6180,19 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>21</v>
@@ -6190,14 +6212,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>310</v>
+        <v>108</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6210,26 +6232,24 @@
         <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>311</v>
+        <v>110</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>312</v>
+        <v>111</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="O38" t="s" s="2">
-        <v>313</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6277,7 +6297,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>314</v>
+        <v>116</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6295,7 +6315,7 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
@@ -6316,36 +6336,38 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>263</v>
+        <v>109</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6370,66 +6392,66 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>319</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AA39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>315</v>
-      </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>322</v>
-      </c>
       <c r="B40" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6437,13 +6459,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6452,16 +6474,18 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6485,13 +6509,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6509,10 +6533,10 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>88</v>
@@ -6524,7 +6548,7 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>326</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>327</v>
@@ -6539,7 +6563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>328</v>
       </c>
@@ -6552,13 +6576,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6627,7 +6651,7 @@
         <v>328</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>88</v>
@@ -6639,10 +6663,10 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
@@ -6656,10 +6680,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6670,7 +6694,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6682,17 +6706,15 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N42" t="s" s="2">
         <v>337</v>
       </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6729,23 +6751,25 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -6754,31 +6778,29 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>340</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>343</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6787,10 +6809,10 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6799,16 +6821,16 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6846,19 +6868,17 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6873,30 +6893,30 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>21</v>
@@ -6918,16 +6938,16 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6977,7 +6997,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6992,35 +7012,37 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>88</v>
@@ -7035,15 +7057,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>263</v>
+        <v>356</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7068,13 +7092,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -7092,13 +7116,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -7107,27 +7131,27 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7150,13 +7174,13 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7183,13 +7207,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7207,7 +7231,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7219,30 +7243,30 @@
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AK46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN46" t="s" s="2">
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AO46" t="s" s="2">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>366</v>
-      </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7250,13 +7274,13 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
@@ -7265,13 +7289,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7322,7 +7346,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7334,7 +7358,7 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
@@ -7346,18 +7370,18 @@
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7377,10 +7401,10 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>373</v>
@@ -7437,7 +7461,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7449,7 +7473,7 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>368</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
@@ -7461,18 +7485,18 @@
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AO48" t="s" s="2">
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
         <v>377</v>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="B49" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7483,19 +7507,19 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K49" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>379</v>
@@ -7552,7 +7576,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7567,27 +7591,27 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>376</v>
-      </c>
       <c r="AO49" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7598,10 +7622,10 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7610,13 +7634,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>329</v>
+        <v>378</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7667,7 +7691,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7682,19 +7706,19 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>21</v>
+        <v>387</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -7725,13 +7749,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7788,7 +7812,7 @@
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -7800,19 +7824,19 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AO51" t="s" s="2">
-        <v>21</v>
-      </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>395</v>
       </c>
@@ -7828,10 +7852,10 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
@@ -7912,27 +7936,27 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AO52" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
         <v>401</v>
       </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="B53" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7940,7 +7964,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>80</v>
@@ -7955,17 +7979,15 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8002,17 +8024,19 @@
         <v>21</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AC53" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8027,37 +8051,35 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>21</v>
+        <v>405</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>409</v>
-      </c>
       <c r="B54" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>80</v>
@@ -8072,16 +8094,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8119,19 +8141,17 @@
         <v>21</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8149,7 +8169,7 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -8163,13 +8183,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>21</v>
@@ -8191,16 +8211,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8250,7 +8270,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8268,7 +8288,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -8282,13 +8302,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>21</v>
@@ -8310,16 +8330,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8369,7 +8389,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8387,7 +8407,7 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
@@ -8401,13 +8421,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>21</v>
@@ -8429,16 +8449,16 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8488,7 +8508,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8506,7 +8526,7 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
@@ -8520,13 +8540,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>21</v>
@@ -8548,16 +8568,16 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8607,7 +8627,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8619,32 +8639,34 @@
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>425</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C59" s="2"/>
+      <c r="C59" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8653,10 +8675,10 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
@@ -8665,15 +8687,17 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>302</v>
+        <v>430</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8722,31 +8746,31 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>431</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -8754,10 +8778,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8768,7 +8792,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -8780,13 +8804,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>102</v>
+        <v>308</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>103</v>
+        <v>433</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>104</v>
+        <v>434</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8837,7 +8861,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>105</v>
+        <v>432</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8849,19 +8873,19 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>106</v>
+        <v>435</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>21</v>
+        <v>436</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
@@ -8869,21 +8893,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8895,17 +8919,15 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8954,19 +8976,19 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
@@ -8986,14 +9008,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>310</v>
+        <v>108</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9006,26 +9028,24 @@
         <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>311</v>
+        <v>110</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>312</v>
+        <v>111</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="O62" t="s" s="2">
-        <v>313</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9073,7 +9093,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>314</v>
+        <v>116</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9091,7 +9111,7 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
@@ -9105,42 +9125,46 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>435</v>
+        <v>109</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>436</v>
+        <v>317</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9188,25 +9212,25 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>434</v>
+        <v>320</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>438</v>
+        <v>189</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
@@ -9220,10 +9244,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9231,7 +9255,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>88</v>
@@ -9246,13 +9270,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>263</v>
+        <v>441</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9279,13 +9303,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>442</v>
+        <v>21</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9303,10 +9327,10 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>88</v>
@@ -9321,24 +9345,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>355</v>
+        <v>444</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>444</v>
+        <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>445</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9349,7 +9373,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9361,13 +9385,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9397,11 +9421,11 @@
         <v>154</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="Z65" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="Z65" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9418,13 +9442,13 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
@@ -9436,24 +9460,24 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9476,13 +9500,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9509,13 +9533,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>21</v>
+        <v>455</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>456</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9533,7 +9557,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9572,14 +9596,14 @@
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>460</v>
+        <v>21</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9591,17 +9615,15 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>464</v>
-      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9668,13 +9690,13 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>21</v>
+        <v>464</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>21</v>
@@ -9682,14 +9704,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9767,7 +9789,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9797,8 +9819,125 @@
         <v>21</v>
       </c>
     </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO68">
+  <autoFilter ref="A1:AO69">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9808,7 +9947,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI67">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2576" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2461" uniqueCount="470">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -915,7 +915,7 @@
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-patient)
 </t>
   </si>
   <si>
@@ -1047,7 +1047,7 @@
     <t>MedicationDispense.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
@@ -1084,6 +1084,9 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
@@ -1150,7 +1153,7 @@
     <t>Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-medicationdispense-type-vs</t>
   </si>
   <si>
     <t>.code</t>
@@ -1320,44 +1323,11 @@
 The pharmacist reviews the medication order prior to dispense and updates the dosageInstruction based on the actual product being dispensed.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:extension.value}
+    <t xml:space="preserve">value:extension.value.ofType(CodeableConcept).coding.code}
 </t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
-  </si>
-  <si>
-    <t>MedicationDispense.dosageInstruction:otherDosage</t>
-  </si>
-  <si>
-    <t>otherDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-other-administration}
-</t>
-  </si>
-  <si>
-    <t>How the medication is to be used by the patient or administered by the caregiver</t>
-  </si>
-  <si>
-    <t>MedicationDispense.dosageInstruction:timedDosage</t>
-  </si>
-  <si>
-    <t>timedDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-timed-administration}
-</t>
-  </si>
-  <si>
-    <t>MedicationDispense.dosageInstruction:frequencyDosage</t>
-  </si>
-  <si>
-    <t>frequencyDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-frequency-administration}
-</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction:freitextDosage</t>
@@ -1368,6 +1338,9 @@
   <si>
     <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-freetext-administration}
 </t>
+  </si>
+  <si>
+    <t>How the medication is to be used by the patient or administered by the caregiver</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction:standardDosage</t>
@@ -1850,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO69"/>
+  <dimension ref="A1:AO66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.87890625" customWidth="true" bestFit="true"/>
@@ -1863,7 +1836,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="195.8359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="199.48828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1878,9 +1851,9 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="117.7890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.5859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="33.0546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="50.23046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -6809,10 +6782,10 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6821,16 +6794,16 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6868,14 +6841,14 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>339</v>
@@ -6893,30 +6866,30 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>339</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>21</v>
@@ -6938,16 +6911,16 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7012,30 +6985,30 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>339</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>21</v>
@@ -7057,16 +7030,16 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7131,27 +7104,27 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7177,10 +7150,10 @@
         <v>269</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7207,13 +7180,11 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7231,7 +7202,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7249,24 +7220,24 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7289,13 +7260,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7346,7 +7317,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7358,30 +7329,30 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7404,13 +7375,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7461,7 +7432,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7473,13 +7444,13 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7488,15 +7459,15 @@
         <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7519,13 +7490,13 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7576,7 +7547,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7594,24 +7565,24 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7634,13 +7605,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7691,7 +7662,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7706,27 +7677,27 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7752,10 +7723,10 @@
         <v>335</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7806,7 +7777,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7824,24 +7795,24 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7864,13 +7835,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7921,7 +7892,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7939,13 +7910,13 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -7953,10 +7924,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7967,7 +7938,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>89</v>
@@ -7979,13 +7950,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8036,7 +8007,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8051,10 +8022,10 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
@@ -8063,15 +8034,15 @@
         <v>21</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8094,16 +8065,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8141,17 +8112,17 @@
         <v>21</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8169,7 +8140,7 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -8183,13 +8154,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>21</v>
@@ -8211,16 +8182,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8270,7 +8241,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8288,7 +8259,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -8302,13 +8273,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>21</v>
@@ -8330,16 +8301,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8389,7 +8360,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8401,13 +8372,13 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>423</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
@@ -8419,16 +8390,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8437,10 +8406,10 @@
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -8449,17 +8418,15 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>424</v>
+        <v>308</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8508,13 +8475,13 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
@@ -8526,28 +8493,26 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8556,10 +8521,10 @@
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
@@ -8568,17 +8533,15 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>427</v>
+        <v>102</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>418</v>
+        <v>103</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8627,25 +8590,25 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>408</v>
+        <v>105</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>414</v>
+        <v>106</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
@@ -8657,18 +8620,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8678,7 +8639,7 @@
         <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
@@ -8687,16 +8648,16 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>430</v>
+        <v>109</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>418</v>
+        <v>110</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>411</v>
+        <v>111</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>412</v>
+        <v>112</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8746,7 +8707,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>408</v>
+        <v>116</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8758,13 +8719,13 @@
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>431</v>
+        <v>117</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>414</v>
+        <v>106</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
@@ -8778,42 +8739,46 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>308</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>433</v>
+        <v>317</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8861,31 +8826,31 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>432</v>
+        <v>320</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>435</v>
+        <v>189</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>436</v>
+        <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
@@ -8893,10 +8858,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8904,7 +8869,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>88</v>
@@ -8919,13 +8884,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>102</v>
+        <v>433</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>103</v>
+        <v>434</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>104</v>
+        <v>435</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8976,10 +8941,10 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>105</v>
+        <v>432</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>88</v>
@@ -8988,13 +8953,13 @@
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>106</v>
+        <v>436</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -9008,21 +8973,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -9034,17 +8999,15 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>109</v>
+        <v>269</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>110</v>
+        <v>438</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9069,13 +9032,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>21</v>
+        <v>440</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -9093,46 +9056,46 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>116</v>
+        <v>437</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>106</v>
+        <v>362</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>21</v>
+        <v>443</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>316</v>
+        <v>21</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9145,26 +9108,22 @@
         <v>21</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>109</v>
+        <v>269</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>317</v>
+        <v>445</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9188,13 +9147,13 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -9212,7 +9171,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>320</v>
+        <v>444</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9224,19 +9183,19 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>189</v>
+        <v>449</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>21</v>
+        <v>450</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>21</v>
@@ -9244,10 +9203,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9255,10 +9214,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -9270,13 +9229,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9327,13 +9286,13 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
@@ -9345,13 +9304,13 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>21</v>
+        <v>456</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>21</v>
@@ -9359,21 +9318,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>21</v>
+        <v>458</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9385,15 +9344,17 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>269</v>
+        <v>459</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9418,13 +9379,13 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -9442,13 +9403,13 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
@@ -9460,24 +9421,24 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>361</v>
+        <v>463</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>450</v>
+        <v>21</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>451</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9488,7 +9449,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -9500,15 +9461,17 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>269</v>
+        <v>465</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9533,13 +9496,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>455</v>
+        <v>21</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>456</v>
+        <v>21</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9557,7 +9520,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9575,369 +9538,20 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>458</v>
+        <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO69" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO69">
+  <autoFilter ref="A1:AO66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9947,7 +9561,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1425,7 +1425,7 @@
     <t>Indicates who or what performed the event.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:function}
+    <t xml:space="preserve">value:function.coding.code}
 </t>
   </si>
   <si>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil einer "Durchgeführten Abgabe" eines Arzneimittels aus dem Medikationsplan.</t>
+    <t>Profil einer "Durchgeführten Abgabe" eines Arzneimittels.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -585,7 +585,7 @@
     <t>MedicationDispense.text.status</t>
   </si>
   <si>
-    <t>generated | extensions | additional | empty</t>
+    <t>Siehe Notes - "Regeln für den Inhalt der narrativen Teile in den Notes".</t>
   </si>
   <si>
     <t>The status of the narrative - whether it's entirely generated (from just the defined data or the extensions too), or whether a human authored it and it may contain additional data.</t>
@@ -636,7 +636,7 @@
 </t>
   </si>
   <si>
-    <t>TODO</t>
+    <t>Es sind nur die hier definierten contained Medication-Ressourcen zulässig. Contained (eingebettete) Ressourcen werden nicht separat versioniert, sondern ausschließlich im Rahmen der übergeordneten Ressource versioniert.</t>
   </si>
   <si>
     <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
@@ -673,7 +673,7 @@
 </t>
   </si>
   <si>
-    <t>Vollständige Darstellung der Dosierungsanweisungen</t>
+    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definiert Regeln befüllt.</t>
   </si>
   <si>
     <t>R5: `MedicationDispense.renderedDosageInstruction` (new:markdown)</t>
@@ -1114,7 +1114,7 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>Status der Durchgeführten Abgabe. Mögliche Ausprägungen: [completed | cancelled | entered-in-error ] Bedeutung: completed: Die Durchgeführte Abgabe ist abgeschlossen. | cancelled: Leerabgabe | entered-in-error: Die Durchgeführte Abgabe wird aufgrund falscher Eingabe storniert.</t>
+    <t>Status der Durchgeführten Abgabe. Mögliche Ausprägungen: [completed | cancelled | entered-in-error ] Bedeutung: completed: Die Durchgeführte Abgabe ist abgeschlossen (Einzel- oder Teilabgabe durchgeführt) | cancelled: Leerabgabe wird durchgeführt | entered-in-error: Die Durchgeführte Abgabe wird aufgrund eines Fehlers storniert.</t>
   </si>
   <si>
     <t>A code specifying the state of the set of dispense events.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -798,7 +798,7 @@
 </t>
   </si>
   <si>
-    <t>Datum der Statusänderung. Dies ist nur bei einem Status von: cancelled | entered-in-error | stopped relevant.</t>
+    <t>Datum der Statusänderung. Dies ist nur bei einem Status von entered-in-error relevant.</t>
   </si>
   <si>
     <t>R5: `MedicationDispense.statusChanged` (new:dateTime)</t>
@@ -839,7 +839,7 @@
 </t>
   </si>
   <si>
-    <t>Als groupIdentifier dient der e-Med GroupIdentifier der zugehörigen Geplanten Abgabe (wird auch im e-Rezept mitgeführt).</t>
+    <t>Als groupIdentifier dient der "e-Med GroupIdentifier" der zugehörigen Geplanten Abgabe (wird auch im e-Rezept mitgeführt).</t>
   </si>
   <si>
     <t>AT ELGA e-Medikation Extension, die den e-Med GroupIdentifier beinhaltet.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -673,7 +673,7 @@
 </t>
   </si>
   <si>
-    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definiert Regeln befüllt.</t>
+    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definierten Regeln befüllt..</t>
   </si>
   <si>
     <t>R5: `MedicationDispense.renderedDosageInstruction` (new:markdown)</t>
@@ -753,7 +753,7 @@
 </t>
   </si>
   <si>
-    <t>Datum und Uhrzeit, zu denen die Abgabe erfasst wurde. Dies muss nicht unbedingt mit dem Zeitpunkt übereinstimmen, zu dem das Medikament dem Patienten ausgehändigt wurde (z.B. bei Nacherfassung der Abgabe).</t>
+    <t>Datum und Uhrzeit, zu denen die Geplante Abgabe erfasst wurde.</t>
   </si>
   <si>
     <t>R5: `MedicationDispense.recorded` (new:dateTime)</t>
@@ -1194,7 +1194,7 @@
 </t>
   </si>
   <si>
-    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als conditional reference dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
+    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als Conditional Reference dokumentiert. Diese kann, sofern ein zugehöriger Planeintrag und eine Geplante Abgabe vorliegen, von der dort angegebenen Medikation abweichen.</t>
   </si>
   <si>
     <t>Identifies the medication being administered. This is either a link to a resource representing the details of the medication or a simple attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -1308,7 +1308,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den die Geplante Abgabe ausgestellt werden soll (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
+    <t>ELGA-Teilnehmer, für den die Durchgeführte Abgabe dokumentiert wird.</t>
   </si>
   <si>
     <t>A link to a resource representing the person or the group to whom the medication will be given.</t>
@@ -1351,9 +1351,6 @@
   </si>
   <si>
     <t>MedicationDispense.subject.identifier.use</t>
-  </si>
-  <si>
-    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>MedicationDispense.subject.identifier.type</t>
@@ -1419,7 +1416,7 @@
 </t>
   </si>
   <si>
-    <t>Durchführende Person</t>
+    <t>Who performed event</t>
   </si>
   <si>
     <t>Indicates who or what performed the event.</t>
@@ -1467,7 +1464,7 @@
     <t>MedicationDispense.performer.function</t>
   </si>
   <si>
-    <t>Rolle der Person, die die Abgabe durchgeführt hat.</t>
+    <t>Who performed the dispense and what they did</t>
   </si>
   <si>
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
@@ -1489,8 +1486,7 @@
 </t>
   </si>
   <si>
-    <t>Refrenz auf Practitioner, PractitionerRole, Organization,der/die die Durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
-auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
+    <t>Individual who was performing</t>
   </si>
   <si>
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
@@ -1508,9 +1504,6 @@
     <t>dispenseGDA</t>
   </si>
   <si>
-    <t>Who performed event</t>
-  </si>
-  <si>
     <t>MedicationDispense.performer:dispenseGDA.id</t>
   </si>
   <si>
@@ -1523,7 +1516,7 @@
     <t>MedicationDispense.performer:dispenseGDA.function</t>
   </si>
   <si>
-    <t>Who performed the dispense and what they did</t>
+    <t>Rolle des der Abgabe durchführenden GDA. Fester Wert: dispenseGDA.</t>
   </si>
   <si>
     <t>A code describing the role an individual played in dispensing a medication.</t>
@@ -1750,7 +1743,7 @@
 </t>
   </si>
   <si>
-    <t>Individual who was performing</t>
+    <t>GDA, der die Abgabe durchführt und verantwortet.</t>
   </si>
   <si>
     <t>MedicationDispense.performer:referenceGDA</t>
@@ -1771,6 +1764,9 @@
     <t>MedicationDispense.performer:referenceGDA.function</t>
   </si>
   <si>
+    <t>Rolle des den Planeintrag nachträglich referenzierenden GDA. Fester Wert: referenceGDA.</t>
+  </si>
+  <si>
     <t>MedicationDispense.performer:referenceGDA.function.id</t>
   </si>
   <si>
@@ -1805,6 +1801,9 @@
   </si>
   <si>
     <t>MedicationDispense.performer:referenceGDA.actor</t>
+  </si>
+  <si>
+    <t>GDA, der nachträglich eine Referenz zu einem Planeintrag herstellt.</t>
   </si>
   <si>
     <t>MedicationDispense.location</t>
@@ -1833,9 +1832,8 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf zugehörige Geplante Abgabe (MedicationRequest), sofern diese existiert bzw. 
-Planeintrag (MedicationRequest). Es muss nicht zwingend eine Geplante Abgabe referenziert werden, da es auch durchgeführte 
-Abgaben ohne Geplante Abgabe geben kann (z.B. Notfall oder OTC-Medikation).</t>
+    <t>Verpflichtende Referenzen auf zugehörige Geplante Abgabe (MedicationRequest) bzw. zugehörigen 
+Planeintrag (MedicationRequest), sofern diese existieren.</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
@@ -1886,7 +1884,7 @@
     <t>MedicationDispense.type</t>
   </si>
   <si>
-    <t>Art der Abgabe (z.B. für Teilabgaben). Mögliche Ausprägungen: [FFC | FFP | RFP | RFC | EM]. Bedeutung: FFC: First Fill - Complete | FFP: First Fill - Part Fill | RFP: Refill - Part Fill | RFC: Refill - Complete | EM: Emergency Supply.</t>
+    <t>Art der Abgabe. Mögliche Ausprägungen: [FFC | FFP | RFP | RFC | EM]. Bedeutung: FFC: First Fill - Complete (Beendigung einer Einzelabgabe) | FFP: First Fill - Part Fill (1. Teilabgabe oder Besorgerprozess) | RFP: Refill - Part Fill (weitere Teilabgabe) | RFC: Refill - Complete (letzte Teilabgabe) | EM: Emergency Supply.</t>
   </si>
   <si>
     <t>Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
@@ -1969,7 +1967,7 @@
     <t>MedicationDispense.whenHandedOver</t>
   </si>
   <si>
-    <t>Der Zeitpunkt, zu dem das abgegebene Produkt dem Patienten oder seinem Vertreter zur Verfügung gestellt wurde.</t>
+    <t>Der Zeitpunkt, zu dem das Arzneimittel aushändigt wurde. Kann vom Erstellzeitpunkt der Durchgeführten Abgabe abweichen (z.B. bei Nacherfassung der Abgabe).</t>
   </si>
   <si>
     <t>The time the dispensed product was provided to the patient or their representative.</t>
@@ -2025,7 +2023,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zur Abgabe, die nicht anders dokumentiert werden kann.</t>
+    <t>Zusätzliche Informationen zur Abgabe, die nicht die Dosierung betreffen.</t>
   </si>
   <si>
     <t>Extra information about the dispense that could not be conveyed in the other attributes.</t>
@@ -2105,8 +2103,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, wie das abgegebene Arzneimittel vom Patienten einzunehmen ist. 
-Der Apotheker überprüft die Medikamentenverordnung vor der Abgabe und passt die Dosierungsanweisung gegebenenfalls auf Grundlage des tatsächlich abgegebenen Produkts an.</t>
+    <t>Gibt an, wie das abgegebene Arzneimittel vom Patienten einzunehmen ist. Diese kann, sofern ein zugehöriger Planeintrag und eine Geplante Abgabe vorliegen, von der dort angegebenen Dosierung abweichen.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -10845,7 +10842,7 @@
         <v>164</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>430</v>
+        <v>279</v>
       </c>
       <c r="M71" t="s" s="2">
         <v>280</v>
@@ -10935,10 +10932,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11054,10 +11051,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11173,10 +11170,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11290,10 +11287,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11405,10 +11402,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11522,10 +11519,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11639,10 +11636,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11665,13 +11662,13 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11722,7 +11719,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11737,10 +11734,10 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AL78" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>21</v>
@@ -11754,10 +11751,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11780,13 +11777,13 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11837,7 +11834,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11855,10 +11852,10 @@
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -11869,10 +11866,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11895,13 +11892,13 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11940,17 +11937,17 @@
         <v>21</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AC80" s="2"/>
       <c r="AD80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11965,10 +11962,10 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL80" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>21</v>
@@ -11982,10 +11979,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12097,10 +12094,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12214,14 +12211,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12243,16 +12240,16 @@
         <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -12301,7 +12298,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12333,10 +12330,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12362,14 +12359,14 @@
         <v>289</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -12398,7 +12395,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>21</v>
@@ -12416,7 +12413,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12434,7 +12431,7 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
@@ -12448,10 +12445,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12474,13 +12471,13 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12531,7 +12528,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>88</v>
@@ -12546,10 +12543,10 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AL85" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
@@ -12563,13 +12560,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C86" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>21</v>
@@ -12591,13 +12588,13 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L86" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="M86" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12648,7 +12645,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12663,10 +12660,10 @@
         <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL86" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>21</v>
@@ -12680,10 +12677,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12795,10 +12792,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12912,10 +12909,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12995,7 +12992,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13027,10 +13024,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13056,14 +13053,14 @@
         <v>289</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -13091,10 +13088,10 @@
         <v>154</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>21</v>
@@ -13112,7 +13109,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13130,7 +13127,7 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>21</v>
@@ -13144,10 +13141,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13259,10 +13256,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13376,10 +13373,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13405,16 +13402,16 @@
         <v>142</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -13463,7 +13460,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13481,7 +13478,7 @@
         <v>21</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>21</v>
@@ -13490,15 +13487,15 @@
         <v>21</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13610,10 +13607,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13727,10 +13724,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13756,16 +13753,16 @@
         <v>130</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -13775,7 +13772,7 @@
         <v>21</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>21</v>
@@ -13814,7 +13811,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13832,7 +13829,7 @@
         <v>21</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>21</v>
@@ -13841,15 +13838,15 @@
         <v>21</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13875,13 +13872,13 @@
         <v>102</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13931,7 +13928,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13949,7 +13946,7 @@
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>21</v>
@@ -13958,15 +13955,15 @@
         <v>21</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13992,14 +13989,14 @@
         <v>164</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>21</v>
@@ -14009,7 +14006,7 @@
         <v>21</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>21</v>
@@ -14048,7 +14045,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14066,7 +14063,7 @@
         <v>21</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>21</v>
@@ -14075,15 +14072,15 @@
         <v>21</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14109,14 +14106,14 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -14165,7 +14162,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14183,7 +14180,7 @@
         <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>21</v>
@@ -14192,15 +14189,15 @@
         <v>21</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14223,19 +14220,19 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -14284,7 +14281,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14302,7 +14299,7 @@
         <v>21</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>21</v>
@@ -14311,15 +14308,15 @@
         <v>21</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14345,16 +14342,16 @@
         <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14403,7 +14400,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14421,7 +14418,7 @@
         <v>21</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>21</v>
@@ -14430,15 +14427,15 @@
         <v>21</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14461,13 +14458,13 @@
         <v>21</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14518,7 +14515,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>88</v>
@@ -14533,10 +14530,10 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>21</v>
@@ -14550,13 +14547,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>21</v>
@@ -14578,13 +14575,13 @@
         <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L103" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="M103" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14635,7 +14632,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14650,10 +14647,10 @@
         <v>100</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL103" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>21</v>
@@ -14667,10 +14664,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14782,10 +14779,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14899,10 +14896,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14982,7 +14979,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15014,10 +15011,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15043,14 +15040,14 @@
         <v>289</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>484</v>
+        <v>564</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -15078,10 +15075,10 @@
         <v>154</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>21</v>
@@ -15099,7 +15096,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15117,7 +15114,7 @@
         <v>21</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>21</v>
@@ -15131,10 +15128,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15246,10 +15243,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15363,10 +15360,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15392,16 +15389,16 @@
         <v>142</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N110" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>21</v>
@@ -15450,7 +15447,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15468,7 +15465,7 @@
         <v>21</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>21</v>
@@ -15477,15 +15474,15 @@
         <v>21</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15597,10 +15594,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15714,10 +15711,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15743,16 +15740,16 @@
         <v>130</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N113" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -15762,7 +15759,7 @@
         <v>21</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>21</v>
@@ -15801,7 +15798,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15819,7 +15816,7 @@
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>21</v>
@@ -15828,15 +15825,15 @@
         <v>21</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15862,13 +15859,13 @@
         <v>102</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N114" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15918,7 +15915,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15936,7 +15933,7 @@
         <v>21</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>21</v>
@@ -15945,15 +15942,15 @@
         <v>21</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15979,14 +15976,14 @@
         <v>164</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>21</v>
@@ -15996,7 +15993,7 @@
         <v>21</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>21</v>
@@ -16035,7 +16032,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16053,7 +16050,7 @@
         <v>21</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>21</v>
@@ -16062,15 +16059,15 @@
         <v>21</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16096,14 +16093,14 @@
         <v>102</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>21</v>
@@ -16152,7 +16149,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16170,7 +16167,7 @@
         <v>21</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>21</v>
@@ -16179,15 +16176,15 @@
         <v>21</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16210,19 +16207,19 @@
         <v>89</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="O117" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
@@ -16271,7 +16268,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16289,7 +16286,7 @@
         <v>21</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>21</v>
@@ -16298,15 +16295,15 @@
         <v>21</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16332,16 +16329,16 @@
         <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N118" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>21</v>
@@ -16390,7 +16387,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16408,7 +16405,7 @@
         <v>21</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>21</v>
@@ -16417,15 +16414,15 @@
         <v>21</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16448,13 +16445,13 @@
         <v>21</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>559</v>
+        <v>577</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16505,7 +16502,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>88</v>
@@ -16520,10 +16517,10 @@
         <v>100</v>
       </c>
       <c r="AK119" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AL119" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>21</v>
@@ -16732,7 +16729,7 @@
         <v>21</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AF121" t="s" s="2">
         <v>583</v>
@@ -18582,7 +18579,7 @@
         <v>21</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AF137" t="s" s="2">
         <v>670</v>
@@ -18881,7 +18878,7 @@
         <v>21</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L140" t="s" s="2">
         <v>686</v>
@@ -19209,7 +19206,7 @@
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -19231,16 +19228,16 @@
         <v>109</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>21</v>
@@ -19289,7 +19286,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19347,7 +19344,7 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="L144" t="s" s="2">
         <v>694</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1482,7 +1482,7 @@
     <t>MedicationDispense.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole)
 </t>
   </si>
   <si>
@@ -2621,7 +2621,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="199.48828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="180.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil einer "Durchgeführten Abgabe" eines Arzneimittels.</t>
+    <t>Profil einer Durchgeführten Abgabe eines Arzneimittels.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5514" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5512" uniqueCount="729">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1444,20 +1444,6 @@
     <t>MedicationDispense.performer.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
@@ -1737,10 +1723,6 @@
   </si>
   <si>
     <t>MedicationDispense.performer:dispenseGDA.actor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
-</t>
   </si>
   <si>
     <t>GDA, der die Abgabe durchführt und verantwortet.</t>
@@ -2169,6 +2151,20 @@
   </si>
   <si>
     <t>MedicationDispense.substitution.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>MedicationDispense.substitution.wasSubstituted</t>
@@ -5010,7 +5006,7 @@
         <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
@@ -11880,7 +11876,7 @@
         <v>88</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>89</v>
@@ -12218,14 +12214,14 @@
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>459</v>
+        <v>21</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -12240,17 +12236,13 @@
         <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>460</v>
+        <v>336</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>21</v>
       </c>
@@ -12298,7 +12290,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12316,7 +12308,7 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
@@ -12328,12 +12320,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12347,7 +12339,7 @@
         <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>21</v>
@@ -12359,14 +12351,14 @@
         <v>289</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -12395,7 +12387,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>21</v>
@@ -12413,7 +12405,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12431,7 +12423,7 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
@@ -12443,12 +12435,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12462,7 +12454,7 @@
         <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>21</v>
@@ -12471,13 +12463,13 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12528,7 +12520,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>88</v>
@@ -12543,10 +12535,10 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
@@ -12560,13 +12552,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>448</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>21</v>
@@ -12677,7 +12669,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>456</v>
@@ -12792,7 +12784,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>457</v>
@@ -12909,7 +12901,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>458</v>
@@ -12992,7 +12984,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13024,10 +13016,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13053,14 +13045,14 @@
         <v>289</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -13088,10 +13080,10 @@
         <v>154</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>21</v>
@@ -13109,7 +13101,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13127,7 +13119,7 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>21</v>
@@ -13141,10 +13133,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13256,10 +13248,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13373,10 +13365,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13402,16 +13394,16 @@
         <v>142</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -13460,7 +13452,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13478,7 +13470,7 @@
         <v>21</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>21</v>
@@ -13487,15 +13479,15 @@
         <v>21</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13607,10 +13599,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13724,10 +13716,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13753,16 +13745,16 @@
         <v>130</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -13772,7 +13764,7 @@
         <v>21</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>21</v>
@@ -13811,7 +13803,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13829,7 +13821,7 @@
         <v>21</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>21</v>
@@ -13838,15 +13830,15 @@
         <v>21</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13872,13 +13864,13 @@
         <v>102</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13928,7 +13920,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13946,7 +13938,7 @@
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>21</v>
@@ -13955,15 +13947,15 @@
         <v>21</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13989,14 +13981,14 @@
         <v>164</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>21</v>
@@ -14006,7 +13998,7 @@
         <v>21</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>21</v>
@@ -14045,7 +14037,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14063,7 +14055,7 @@
         <v>21</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>21</v>
@@ -14072,15 +14064,15 @@
         <v>21</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14106,14 +14098,14 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -14162,7 +14154,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14180,7 +14172,7 @@
         <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>21</v>
@@ -14189,15 +14181,15 @@
         <v>21</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14220,19 +14212,19 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="O100" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -14281,7 +14273,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14299,7 +14291,7 @@
         <v>21</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>21</v>
@@ -14308,15 +14300,15 @@
         <v>21</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14342,16 +14334,16 @@
         <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14400,7 +14392,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14418,7 +14410,7 @@
         <v>21</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>21</v>
@@ -14427,15 +14419,15 @@
         <v>21</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14458,13 +14450,13 @@
         <v>21</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>556</v>
+        <v>467</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14515,7 +14507,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>88</v>
@@ -14530,10 +14522,10 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>21</v>
@@ -14547,13 +14539,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>448</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>21</v>
@@ -14563,7 +14555,7 @@
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>89</v>
@@ -14664,7 +14656,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>456</v>
@@ -14779,7 +14771,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>457</v>
@@ -14896,7 +14888,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>458</v>
@@ -14979,7 +14971,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15011,10 +15003,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15040,14 +15032,14 @@
         <v>289</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -15075,10 +15067,10 @@
         <v>154</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>21</v>
@@ -15096,7 +15088,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15114,7 +15106,7 @@
         <v>21</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>21</v>
@@ -15128,10 +15120,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15243,10 +15235,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15360,10 +15352,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15389,16 +15381,16 @@
         <v>142</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>21</v>
@@ -15447,7 +15439,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15465,7 +15457,7 @@
         <v>21</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>21</v>
@@ -15474,15 +15466,15 @@
         <v>21</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15594,10 +15586,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15711,10 +15703,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15740,16 +15732,16 @@
         <v>130</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -15759,7 +15751,7 @@
         <v>21</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>21</v>
@@ -15798,7 +15790,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15816,7 +15808,7 @@
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>21</v>
@@ -15825,15 +15817,15 @@
         <v>21</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15859,13 +15851,13 @@
         <v>102</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15915,7 +15907,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15933,7 +15925,7 @@
         <v>21</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>21</v>
@@ -15942,15 +15934,15 @@
         <v>21</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15976,14 +15968,14 @@
         <v>164</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>21</v>
@@ -15993,7 +15985,7 @@
         <v>21</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>21</v>
@@ -16032,7 +16024,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16050,7 +16042,7 @@
         <v>21</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>21</v>
@@ -16059,15 +16051,15 @@
         <v>21</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16093,14 +16085,14 @@
         <v>102</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>21</v>
@@ -16149,7 +16141,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16167,7 +16159,7 @@
         <v>21</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>21</v>
@@ -16176,15 +16168,15 @@
         <v>21</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16207,19 +16199,19 @@
         <v>89</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="O117" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
@@ -16268,7 +16260,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16286,7 +16278,7 @@
         <v>21</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>21</v>
@@ -16295,15 +16287,15 @@
         <v>21</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16329,16 +16321,16 @@
         <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>21</v>
@@ -16387,7 +16379,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16405,7 +16397,7 @@
         <v>21</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>21</v>
@@ -16414,15 +16406,15 @@
         <v>21</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16445,13 +16437,13 @@
         <v>21</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>556</v>
+        <v>467</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16502,7 +16494,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>88</v>
@@ -16517,10 +16509,10 @@
         <v>100</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>21</v>
@@ -16534,10 +16526,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16560,13 +16552,13 @@
         <v>21</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16617,7 +16609,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16635,7 +16627,7 @@
         <v>21</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>21</v>
@@ -16649,10 +16641,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16663,7 +16655,7 @@
         <v>79</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>89</v>
@@ -16675,16 +16667,16 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16722,7 +16714,7 @@
         <v>21</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="AC121" s="2"/>
       <c r="AD121" t="s" s="2">
@@ -16732,7 +16724,7 @@
         <v>453</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16747,30 +16739,30 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>21</v>
@@ -16792,16 +16784,16 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16851,7 +16843,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16866,30 +16858,30 @@
         <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>21</v>
@@ -16911,16 +16903,16 @@
         <v>21</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -16970,7 +16962,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16985,27 +16977,27 @@
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17031,10 +17023,10 @@
         <v>289</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17065,7 +17057,7 @@
       </c>
       <c r="Y124" s="2"/>
       <c r="Z124" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>21</v>
@@ -17083,7 +17075,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17101,24 +17093,24 @@
         <v>21</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17141,13 +17133,13 @@
         <v>21</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -17198,42 +17190,42 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL125" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="AG125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>613</v>
-      </c>
       <c r="AM125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17256,13 +17248,13 @@
         <v>21</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17313,7 +17305,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17325,13 +17317,13 @@
         <v>21</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>21</v>
@@ -17340,15 +17332,15 @@
         <v>21</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>620</v>
+        <v>615</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17374,10 +17366,10 @@
         <v>244</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17428,7 +17420,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17446,24 +17438,24 @@
         <v>21</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17489,10 +17481,10 @@
         <v>244</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17543,7 +17535,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17558,27 +17550,27 @@
         <v>100</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17601,13 +17593,13 @@
         <v>21</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17658,7 +17650,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17676,24 +17668,24 @@
         <v>21</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>637</v>
+        <v>632</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17716,13 +17708,13 @@
         <v>21</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17773,7 +17765,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17791,13 +17783,13 @@
         <v>21</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>21</v>
@@ -17805,10 +17797,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17831,13 +17823,13 @@
         <v>21</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17888,7 +17880,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17903,10 +17895,10 @@
         <v>100</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>21</v>
@@ -17915,15 +17907,15 @@
         <v>21</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18035,10 +18027,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18152,10 +18144,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18178,16 +18170,16 @@
         <v>89</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18237,7 +18229,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18255,7 +18247,7 @@
         <v>21</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>21</v>
@@ -18269,10 +18261,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18298,10 +18290,10 @@
         <v>244</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18352,7 +18344,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18370,7 +18362,7 @@
         <v>21</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>21</v>
@@ -18384,10 +18376,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18413,10 +18405,10 @@
         <v>228</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18467,7 +18459,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>88</v>
@@ -18485,7 +18477,7 @@
         <v>21</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>21</v>
@@ -18499,10 +18491,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18525,16 +18517,16 @@
         <v>21</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18572,7 +18564,7 @@
         <v>21</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="AC137" s="2"/>
       <c r="AD137" t="s" s="2">
@@ -18582,7 +18574,7 @@
         <v>453</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18600,7 +18592,7 @@
         <v>21</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>21</v>
@@ -18614,13 +18606,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>21</v>
@@ -18642,16 +18634,16 @@
         <v>21</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18701,7 +18693,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18719,7 +18711,7 @@
         <v>21</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>21</v>
@@ -18733,13 +18725,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>21</v>
@@ -18761,16 +18753,16 @@
         <v>21</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18820,7 +18812,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -18832,13 +18824,13 @@
         <v>21</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>21</v>
@@ -18852,10 +18844,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18881,10 +18873,10 @@
         <v>449</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18935,7 +18927,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18953,13 +18945,13 @@
         <v>21</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>21</v>
@@ -18967,10 +18959,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19082,10 +19074,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19199,14 +19191,14 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>459</v>
+        <v>688</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -19228,16 +19220,16 @@
         <v>109</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>460</v>
+        <v>689</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>461</v>
+        <v>690</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>462</v>
+        <v>691</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>21</v>
@@ -19286,7 +19278,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19318,10 +19310,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19344,13 +19336,13 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -19401,7 +19393,7 @@
         <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>88</v>
@@ -19419,7 +19411,7 @@
         <v>21</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>21</v>
@@ -19433,10 +19425,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19462,10 +19454,10 @@
         <v>289</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -19495,11 +19487,11 @@
         <v>154</v>
       </c>
       <c r="Y145" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="Z145" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="Z145" t="s" s="2">
-        <v>701</v>
-      </c>
       <c r="AA145" t="s" s="2">
         <v>21</v>
       </c>
@@ -19516,7 +19508,7 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19534,24 +19526,24 @@
         <v>21</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN145" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AO145" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="AO145" t="s" s="2">
-        <v>703</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19577,10 +19569,10 @@
         <v>289</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -19610,11 +19602,11 @@
         <v>154</v>
       </c>
       <c r="Y146" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="Z146" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="Z146" t="s" s="2">
-        <v>708</v>
-      </c>
       <c r="AA146" t="s" s="2">
         <v>21</v>
       </c>
@@ -19631,7 +19623,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -19649,13 +19641,13 @@
         <v>21</v>
       </c>
       <c r="AL146" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN146" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>21</v>
@@ -19663,10 +19655,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19689,13 +19681,13 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -19746,7 +19738,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19764,13 +19756,13 @@
         <v>21</v>
       </c>
       <c r="AL147" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN147" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="AM147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>21</v>
@@ -19778,14 +19770,14 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -19804,16 +19796,16 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="L148" t="s" s="2">
+      <c r="M148" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19863,7 +19855,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19881,7 +19873,7 @@
         <v>21</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>21</v>
@@ -19895,10 +19887,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19921,16 +19913,16 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="L149" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19980,7 +19972,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -19998,7 +19990,7 @@
         <v>21</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -561,7 +561,7 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
+    <t>Narrative - wird immer durch die Fachanwendung generiert.</t>
   </si>
   <si>
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5512" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5511" uniqueCount="728">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1123,10 +1123,7 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>A coded concept specifying the state of the dispense event.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetMedicationDispenseStatusVS</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -8774,11 +8771,9 @@
       <c r="X53" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y53" t="s" s="2">
+      <c r="Y53" s="2"/>
+      <c r="Z53" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8811,16 +8806,16 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -8828,10 +8823,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8854,13 +8849,13 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8890,11 +8885,11 @@
         <v>154</v>
       </c>
       <c r="Y54" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z54" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8911,7 +8906,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8926,10 +8921,10 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -8943,10 +8938,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8972,13 +8967,13 @@
         <v>289</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9007,11 +9002,11 @@
         <v>168</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>375</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
       </c>
@@ -9028,7 +9023,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9046,7 +9041,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -9060,10 +9055,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9086,16 +9081,16 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9145,7 +9140,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>88</v>
@@ -9160,27 +9155,27 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AM56" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>386</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9292,10 +9287,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9409,10 +9404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9438,13 +9433,13 @@
         <v>102</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9494,16 +9489,16 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI59" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>100</v>
@@ -9526,10 +9521,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9555,13 +9550,13 @@
         <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9590,28 +9585,28 @@
         <v>146</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z60" t="s" s="2">
+      <c r="AA60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9643,10 +9638,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9672,13 +9667,13 @@
         <v>270</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9728,7 +9723,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9746,7 +9741,7 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -9760,10 +9755,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9789,13 +9784,13 @@
         <v>102</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9845,7 +9840,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9877,10 +9872,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9903,16 +9898,16 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9962,7 +9957,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9977,27 +9972,27 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>421</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10109,10 +10104,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10226,10 +10221,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10255,13 +10250,13 @@
         <v>102</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10311,16 +10306,16 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI66" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>100</v>
@@ -10343,10 +10338,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10372,13 +10367,13 @@
         <v>130</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10407,28 +10402,28 @@
         <v>146</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z67" t="s" s="2">
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10460,10 +10455,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10489,13 +10484,13 @@
         <v>270</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10545,7 +10540,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10563,7 +10558,7 @@
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>21</v>
@@ -10577,10 +10572,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10692,10 +10687,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10809,10 +10804,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10928,10 +10923,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11047,10 +11042,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11166,10 +11161,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11283,10 +11278,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11398,10 +11393,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11515,10 +11510,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11544,13 +11539,13 @@
         <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11600,7 +11595,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11632,10 +11627,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11658,13 +11653,13 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11715,7 +11710,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11730,10 +11725,10 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL78" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>21</v>
@@ -11747,10 +11742,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11773,13 +11768,13 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11830,7 +11825,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11848,10 +11843,10 @@
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -11862,10 +11857,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11888,13 +11883,13 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11933,17 +11928,17 @@
         <v>21</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AC80" s="2"/>
       <c r="AD80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11958,10 +11953,10 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL80" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>21</v>
@@ -11975,10 +11970,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12090,10 +12085,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12207,10 +12202,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12290,7 +12285,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12322,10 +12317,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12351,14 +12346,14 @@
         <v>289</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -12387,7 +12382,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>21</v>
@@ -12405,7 +12400,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12423,7 +12418,7 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
@@ -12437,10 +12432,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12463,13 +12458,13 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12520,7 +12515,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>88</v>
@@ -12535,10 +12530,10 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL85" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
@@ -12552,13 +12547,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C86" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>21</v>
@@ -12580,13 +12575,13 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12637,7 +12632,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12652,10 +12647,10 @@
         <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL86" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>21</v>
@@ -12669,10 +12664,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12784,10 +12779,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12901,10 +12896,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12984,7 +12979,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13016,10 +13011,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13045,14 +13040,14 @@
         <v>289</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -13080,11 +13075,11 @@
         <v>154</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>480</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>21</v>
       </c>
@@ -13101,7 +13096,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13119,7 +13114,7 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>21</v>
@@ -13133,10 +13128,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13248,10 +13243,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13365,10 +13360,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13394,16 +13389,16 @@
         <v>142</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -13452,7 +13447,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13470,24 +13465,24 @@
         <v>21</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>493</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13599,10 +13594,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13716,10 +13711,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13745,16 +13740,16 @@
         <v>130</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -13764,46 +13759,46 @@
         <v>21</v>
       </c>
       <c r="S96" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF96" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13821,24 +13816,24 @@
         <v>21</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>507</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13864,13 +13859,13 @@
         <v>102</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13920,7 +13915,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13938,24 +13933,24 @@
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>515</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13981,14 +13976,14 @@
         <v>164</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>21</v>
@@ -13998,7 +13993,7 @@
         <v>21</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>21</v>
@@ -14037,7 +14032,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14055,24 +14050,24 @@
         <v>21</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>523</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14098,14 +14093,14 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -14154,7 +14149,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14172,24 +14167,24 @@
         <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>531</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14212,19 +14207,19 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -14273,7 +14268,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14291,24 +14286,24 @@
         <v>21</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO100" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>541</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14334,16 +14329,16 @@
         <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14392,7 +14387,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14410,24 +14405,24 @@
         <v>21</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO101" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>550</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14450,13 +14445,13 @@
         <v>21</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14507,7 +14502,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>88</v>
@@ -14522,10 +14517,10 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>21</v>
@@ -14539,13 +14534,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>21</v>
@@ -14567,13 +14562,13 @@
         <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14624,7 +14619,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14639,10 +14634,10 @@
         <v>100</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL103" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>21</v>
@@ -14656,10 +14651,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14771,10 +14766,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14888,10 +14883,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14971,7 +14966,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15003,10 +14998,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15032,14 +15027,14 @@
         <v>289</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -15067,11 +15062,11 @@
         <v>154</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="Z107" t="s" s="2">
-        <v>480</v>
-      </c>
       <c r="AA107" t="s" s="2">
         <v>21</v>
       </c>
@@ -15088,7 +15083,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15106,7 +15101,7 @@
         <v>21</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>21</v>
@@ -15120,10 +15115,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15235,10 +15230,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15352,10 +15347,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15381,16 +15376,16 @@
         <v>142</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>21</v>
@@ -15439,7 +15434,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15457,24 +15452,24 @@
         <v>21</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO110" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>493</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15586,10 +15581,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15703,10 +15698,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15732,16 +15727,16 @@
         <v>130</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -15751,46 +15746,46 @@
         <v>21</v>
       </c>
       <c r="S113" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF113" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15808,24 +15803,24 @@
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO113" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>507</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15851,13 +15846,13 @@
         <v>102</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15907,7 +15902,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15925,24 +15920,24 @@
         <v>21</v>
       </c>
       <c r="AL114" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO114" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>515</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15968,14 +15963,14 @@
         <v>164</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>21</v>
@@ -15985,7 +15980,7 @@
         <v>21</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>21</v>
@@ -16024,7 +16019,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16042,24 +16037,24 @@
         <v>21</v>
       </c>
       <c r="AL115" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO115" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>523</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16085,14 +16080,14 @@
         <v>102</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>21</v>
@@ -16141,7 +16136,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16159,24 +16154,24 @@
         <v>21</v>
       </c>
       <c r="AL116" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO116" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>531</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16199,19 +16194,19 @@
         <v>89</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="N117" t="s" s="2">
+      <c r="O117" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
@@ -16260,7 +16255,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16278,24 +16273,24 @@
         <v>21</v>
       </c>
       <c r="AL117" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO117" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>541</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16321,16 +16316,16 @@
         <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>21</v>
@@ -16379,7 +16374,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16397,24 +16392,24 @@
         <v>21</v>
       </c>
       <c r="AL118" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO118" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>550</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16437,13 +16432,13 @@
         <v>21</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16494,7 +16489,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>88</v>
@@ -16509,10 +16504,10 @@
         <v>100</v>
       </c>
       <c r="AK119" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL119" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>21</v>
@@ -16526,10 +16521,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16552,13 +16547,13 @@
         <v>21</v>
       </c>
       <c r="K120" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="L120" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="L120" t="s" s="2">
+      <c r="M120" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16609,7 +16604,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16627,7 +16622,7 @@
         <v>21</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>21</v>
@@ -16641,10 +16636,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16655,7 +16650,7 @@
         <v>79</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>89</v>
@@ -16667,16 +16662,16 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16714,17 +16709,17 @@
         <v>21</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AC121" s="2"/>
       <c r="AD121" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16739,30 +16734,30 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AL121" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AL121" t="s" s="2">
+      <c r="AM121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AM121" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN121" t="s" s="2">
+      <c r="AO121" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>588</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C122" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>21</v>
@@ -16784,16 +16779,16 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="L122" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="M122" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N122" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16843,7 +16838,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16858,30 +16853,30 @@
         <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AL122" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AL122" t="s" s="2">
+      <c r="AM122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AM122" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN122" t="s" s="2">
+      <c r="AO122" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>588</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C123" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>21</v>
@@ -16903,16 +16898,16 @@
         <v>21</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="M123" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N123" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -16962,7 +16957,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16977,27 +16972,27 @@
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AL123" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AL123" t="s" s="2">
+      <c r="AM123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AM123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN123" t="s" s="2">
+      <c r="AO123" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>588</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17023,10 +17018,10 @@
         <v>289</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17057,7 +17052,7 @@
       </c>
       <c r="Y124" s="2"/>
       <c r="Z124" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>21</v>
@@ -17075,7 +17070,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17093,24 +17088,24 @@
         <v>21</v>
       </c>
       <c r="AL124" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="AM124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN124" t="s" s="2">
+      <c r="AO124" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>602</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17133,13 +17128,13 @@
         <v>21</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -17190,7 +17185,7 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17202,30 +17197,30 @@
         <v>21</v>
       </c>
       <c r="AJ125" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL125" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="AK125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL125" t="s" s="2">
+      <c r="AM125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="AM125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN125" t="s" s="2">
+      <c r="AO125" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>610</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17248,13 +17243,13 @@
         <v>21</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17305,7 +17300,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17317,30 +17312,30 @@
         <v>21</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL126" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO126" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>615</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17366,10 +17361,10 @@
         <v>244</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17420,7 +17415,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17438,24 +17433,24 @@
         <v>21</v>
       </c>
       <c r="AL127" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN127" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="AM127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN127" t="s" s="2">
+      <c r="AO127" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>621</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17481,10 +17476,10 @@
         <v>244</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17535,7 +17530,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17550,27 +17545,27 @@
         <v>100</v>
       </c>
       <c r="AK128" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AL128" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AL128" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="AM128" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN128" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AO128" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>621</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17593,13 +17588,13 @@
         <v>21</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17650,7 +17645,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17668,24 +17663,24 @@
         <v>21</v>
       </c>
       <c r="AL129" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN129" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AM129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN129" t="s" s="2">
+      <c r="AO129" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>632</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17708,13 +17703,13 @@
         <v>21</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17765,7 +17760,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17783,13 +17778,13 @@
         <v>21</v>
       </c>
       <c r="AL130" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN130" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>21</v>
@@ -17797,10 +17792,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17823,13 +17818,13 @@
         <v>21</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="L131" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="M131" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17880,7 +17875,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17895,27 +17890,27 @@
         <v>100</v>
       </c>
       <c r="AK131" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AL131" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="AL131" t="s" s="2">
+      <c r="AM131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO131" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>645</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18027,10 +18022,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18144,10 +18139,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18170,16 +18165,16 @@
         <v>89</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18229,7 +18224,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18247,7 +18242,7 @@
         <v>21</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>21</v>
@@ -18261,10 +18256,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18290,10 +18285,10 @@
         <v>244</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18344,7 +18339,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18362,7 +18357,7 @@
         <v>21</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>21</v>
@@ -18376,10 +18371,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18405,10 +18400,10 @@
         <v>228</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18459,7 +18454,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>88</v>
@@ -18477,7 +18472,7 @@
         <v>21</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>21</v>
@@ -18491,10 +18486,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18517,16 +18512,16 @@
         <v>21</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18564,17 +18559,17 @@
         <v>21</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AC137" s="2"/>
       <c r="AD137" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18592,7 +18587,7 @@
         <v>21</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>21</v>
@@ -18606,13 +18601,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C138" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>21</v>
@@ -18634,16 +18629,16 @@
         <v>21</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="L138" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="L138" t="s" s="2">
-        <v>675</v>
-      </c>
       <c r="M138" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="N138" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18693,7 +18688,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18711,7 +18706,7 @@
         <v>21</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>21</v>
@@ -18725,13 +18720,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C139" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>21</v>
@@ -18753,16 +18748,16 @@
         <v>21</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="M139" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="N139" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18812,7 +18807,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -18824,13 +18819,13 @@
         <v>21</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>21</v>
@@ -18844,10 +18839,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18870,13 +18865,13 @@
         <v>21</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18927,7 +18922,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18945,13 +18940,13 @@
         <v>21</v>
       </c>
       <c r="AL140" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN140" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>21</v>
@@ -18959,10 +18954,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19074,10 +19069,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19191,14 +19186,14 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -19220,16 +19215,16 @@
         <v>109</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>21</v>
@@ -19278,7 +19273,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19310,10 +19305,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19336,13 +19331,13 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -19393,7 +19388,7 @@
         <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>88</v>
@@ -19411,7 +19406,7 @@
         <v>21</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>21</v>
@@ -19425,10 +19420,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19454,10 +19449,10 @@
         <v>289</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>697</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>698</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -19487,11 +19482,11 @@
         <v>154</v>
       </c>
       <c r="Y145" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="Z145" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="Z145" t="s" s="2">
-        <v>700</v>
-      </c>
       <c r="AA145" t="s" s="2">
         <v>21</v>
       </c>
@@ -19508,7 +19503,7 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19526,24 +19521,24 @@
         <v>21</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN145" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AO145" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="AO145" t="s" s="2">
-        <v>702</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19569,10 +19564,10 @@
         <v>289</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -19602,11 +19597,11 @@
         <v>154</v>
       </c>
       <c r="Y146" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="Z146" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="Z146" t="s" s="2">
-        <v>707</v>
-      </c>
       <c r="AA146" t="s" s="2">
         <v>21</v>
       </c>
@@ -19623,7 +19618,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -19641,13 +19636,13 @@
         <v>21</v>
       </c>
       <c r="AL146" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN146" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>21</v>
@@ -19655,10 +19650,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19681,13 +19676,13 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -19738,7 +19733,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19756,13 +19751,13 @@
         <v>21</v>
       </c>
       <c r="AL147" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN147" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="AM147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>21</v>
@@ -19770,14 +19765,14 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -19796,16 +19791,16 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="L148" t="s" s="2">
+      <c r="M148" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19855,7 +19850,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19873,7 +19868,7 @@
         <v>21</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>21</v>
@@ -19887,10 +19882,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19913,16 +19908,16 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="L149" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19972,7 +19967,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -19990,7 +19985,7 @@
         <v>21</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1123,7 +1123,7 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetMedicationDispenseStatusVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-medicationdispense-status-vs</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1456,7 +1456,7 @@
     <t>Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetMedicationDispensePerformerFunctionVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-medicationdispense-performer-function-vs</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1577,7 +1577,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/AtElgaEmedValueSetMedicationDispensePerformerFunctionCS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/at-elga-emed-codesystem-medicationdispense-performer-function-cs</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1869,7 +1869,7 @@
     <t>Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-medicationdispense-type-vs</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-medicationdispense-type-vs</t>
   </si>
   <si>
     <t>.code</t>
@@ -2629,7 +2629,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="117.7890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="82.421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="85.2421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="50.23046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -673,7 +673,7 @@
 </t>
   </si>
   <si>
-    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definierten Regeln befüllt..</t>
+    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definierten Regeln befüllt.</t>
   </si>
   <si>
     <t>R5: `MedicationDispense.renderedDosageInstruction` (new:markdown)</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
